--- a/reports/Debug-snowbowl-20260106/For The Day (Actual)_Payroll.xlsx
+++ b/reports/Debug-snowbowl-20260106/For The Day (Actual)_Payroll.xlsx
@@ -14,104 +14,104 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1071" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1084" uniqueCount="249">
   <si>
     <t>eecode</t>
   </si>
   <si>
+    <t>A4BY</t>
+  </si>
+  <si>
+    <t>A0C2</t>
+  </si>
+  <si>
+    <t>A0OV</t>
+  </si>
+  <si>
+    <t>A2C5</t>
+  </si>
+  <si>
+    <t>A31F</t>
+  </si>
+  <si>
+    <t>A3OF</t>
+  </si>
+  <si>
+    <t>I304</t>
+  </si>
+  <si>
+    <t>D816</t>
+  </si>
+  <si>
     <t>A3MX</t>
   </si>
   <si>
-    <t>I304</t>
-  </si>
-  <si>
-    <t>A0C2</t>
-  </si>
-  <si>
-    <t>A0OV</t>
-  </si>
-  <si>
-    <t>A2C5</t>
-  </si>
-  <si>
-    <t>D816</t>
+    <t>D521</t>
+  </si>
+  <si>
+    <t>D528</t>
+  </si>
+  <si>
+    <t>A3OL</t>
+  </si>
+  <si>
+    <t>C346</t>
+  </si>
+  <si>
+    <t>J405</t>
+  </si>
+  <si>
+    <t>A0OU</t>
+  </si>
+  <si>
+    <t>H632</t>
+  </si>
+  <si>
+    <t>A2CL</t>
+  </si>
+  <si>
+    <t>A3ML</t>
+  </si>
+  <si>
+    <t>F627</t>
+  </si>
+  <si>
+    <t>A0BA</t>
+  </si>
+  <si>
+    <t>A11C</t>
+  </si>
+  <si>
+    <t>A1UT</t>
+  </si>
+  <si>
+    <t>A3MS</t>
+  </si>
+  <si>
+    <t>A3OA</t>
+  </si>
+  <si>
+    <t>A749</t>
+  </si>
+  <si>
+    <t>B884</t>
+  </si>
+  <si>
+    <t>D954</t>
+  </si>
+  <si>
+    <t>E483</t>
+  </si>
+  <si>
+    <t>G961</t>
+  </si>
+  <si>
+    <t>A337</t>
   </si>
   <si>
     <t>G693</t>
   </si>
   <si>
-    <t>H632</t>
-  </si>
-  <si>
-    <t>D521</t>
-  </si>
-  <si>
-    <t>D528</t>
-  </si>
-  <si>
-    <t>A0BA</t>
-  </si>
-  <si>
-    <t>A11C</t>
-  </si>
-  <si>
-    <t>A1UT</t>
-  </si>
-  <si>
-    <t>A3OL</t>
-  </si>
-  <si>
-    <t>A3OF</t>
-  </si>
-  <si>
-    <t>C346</t>
-  </si>
-  <si>
-    <t>A0OU</t>
-  </si>
-  <si>
-    <t>A2CL</t>
-  </si>
-  <si>
-    <t>A337</t>
-  </si>
-  <si>
-    <t>A3ML</t>
-  </si>
-  <si>
-    <t>A3MS</t>
-  </si>
-  <si>
-    <t>A3OA</t>
-  </si>
-  <si>
-    <t>A4BY</t>
-  </si>
-  <si>
-    <t>A749</t>
-  </si>
-  <si>
-    <t>B884</t>
-  </si>
-  <si>
-    <t>D954</t>
-  </si>
-  <si>
-    <t>E483</t>
-  </si>
-  <si>
-    <t>F627</t>
-  </si>
-  <si>
-    <t>G961</t>
-  </si>
-  <si>
-    <t>J405</t>
-  </si>
-  <si>
-    <t>A31F</t>
-  </si>
-  <si>
     <t>I384</t>
   </si>
   <si>
@@ -121,222 +121,222 @@
     <t>A3I8</t>
   </si>
   <si>
+    <t>E568</t>
+  </si>
+  <si>
+    <t>A0QK</t>
+  </si>
+  <si>
+    <t>A3IG</t>
+  </si>
+  <si>
+    <t>A35Y</t>
+  </si>
+  <si>
+    <t>A3KD</t>
+  </si>
+  <si>
+    <t>A0QH</t>
+  </si>
+  <si>
+    <t>A3J1</t>
+  </si>
+  <si>
+    <t>J561</t>
+  </si>
+  <si>
+    <t>A3WC</t>
+  </si>
+  <si>
+    <t>E530</t>
+  </si>
+  <si>
     <t>A3IS</t>
   </si>
   <si>
-    <t>A0QK</t>
-  </si>
-  <si>
-    <t>A3IG</t>
-  </si>
-  <si>
-    <t>A35Y</t>
-  </si>
-  <si>
-    <t>E530</t>
-  </si>
-  <si>
-    <t>A3WC</t>
-  </si>
-  <si>
-    <t>J561</t>
-  </si>
-  <si>
-    <t>A0QH</t>
-  </si>
-  <si>
-    <t>A3J1</t>
-  </si>
-  <si>
-    <t>E568</t>
-  </si>
-  <si>
-    <t>A3KD</t>
-  </si>
-  <si>
     <t>F035</t>
   </si>
   <si>
     <t>F703</t>
   </si>
   <si>
+    <t>C215</t>
+  </si>
+  <si>
+    <t>C349</t>
+  </si>
+  <si>
+    <t>I305</t>
+  </si>
+  <si>
     <t>G963</t>
   </si>
   <si>
-    <t>I305</t>
-  </si>
-  <si>
-    <t>C215</t>
-  </si>
-  <si>
-    <t>C349</t>
-  </si>
-  <si>
     <t>B567</t>
   </si>
   <si>
     <t>A20A</t>
   </si>
   <si>
+    <t>C644</t>
+  </si>
+  <si>
+    <t>E893</t>
+  </si>
+  <si>
+    <t>F013</t>
+  </si>
+  <si>
+    <t>A3JT</t>
+  </si>
+  <si>
+    <t>D576</t>
+  </si>
+  <si>
+    <t>E660</t>
+  </si>
+  <si>
+    <t>F124</t>
+  </si>
+  <si>
+    <t>E835</t>
+  </si>
+  <si>
+    <t>G573</t>
+  </si>
+  <si>
+    <t>C232</t>
+  </si>
+  <si>
+    <t>D619</t>
+  </si>
+  <si>
+    <t>G710</t>
+  </si>
+  <si>
+    <t>A1OP</t>
+  </si>
+  <si>
     <t>A3I5</t>
   </si>
   <si>
-    <t>G573</t>
-  </si>
-  <si>
     <t>A278</t>
   </si>
   <si>
-    <t>A1OP</t>
-  </si>
-  <si>
-    <t>D619</t>
-  </si>
-  <si>
-    <t>C644</t>
-  </si>
-  <si>
-    <t>A3JT</t>
-  </si>
-  <si>
-    <t>E835</t>
-  </si>
-  <si>
-    <t>E893</t>
-  </si>
-  <si>
-    <t>F013</t>
-  </si>
-  <si>
-    <t>G710</t>
-  </si>
-  <si>
-    <t>D576</t>
-  </si>
-  <si>
-    <t>E660</t>
-  </si>
-  <si>
-    <t>F124</t>
-  </si>
-  <si>
     <t>H115</t>
   </si>
   <si>
-    <t>C232</t>
+    <t>A2CT</t>
+  </si>
+  <si>
+    <t>A3T9</t>
+  </si>
+  <si>
+    <t>A2CR</t>
+  </si>
+  <si>
+    <t>A4HG</t>
   </si>
   <si>
     <t>A3TB</t>
   </si>
   <si>
+    <t>A3RR</t>
+  </si>
+  <si>
+    <t>A0ZW</t>
+  </si>
+  <si>
     <t>A3RQ</t>
   </si>
   <si>
+    <t>A2FK</t>
+  </si>
+  <si>
+    <t>F959</t>
+  </si>
+  <si>
     <t>A3TE</t>
   </si>
   <si>
-    <t>F959</t>
+    <t>A3TF</t>
   </si>
   <si>
     <t>A3X6</t>
   </si>
   <si>
-    <t>A3RR</t>
-  </si>
-  <si>
-    <t>A0ZW</t>
-  </si>
-  <si>
-    <t>A3TF</t>
-  </si>
-  <si>
-    <t>A4HG</t>
-  </si>
-  <si>
-    <t>A2CR</t>
-  </si>
-  <si>
-    <t>A3T9</t>
-  </si>
-  <si>
     <t>A0TR</t>
   </si>
   <si>
-    <t>A2CT</t>
-  </si>
-  <si>
-    <t>A2FK</t>
-  </si>
-  <si>
     <t>A0QI</t>
   </si>
   <si>
+    <t>E190</t>
+  </si>
+  <si>
+    <t>A2YQ</t>
+  </si>
+  <si>
+    <t>A399</t>
+  </si>
+  <si>
     <t>G730</t>
   </si>
   <si>
-    <t>A399</t>
-  </si>
-  <si>
-    <t>E190</t>
-  </si>
-  <si>
-    <t>A2YQ</t>
+    <t>A2IE</t>
   </si>
   <si>
     <t>H439</t>
   </si>
   <si>
+    <t>A44G</t>
+  </si>
+  <si>
+    <t>A44H</t>
+  </si>
+  <si>
+    <t>A30J</t>
+  </si>
+  <si>
     <t>A3O2</t>
   </si>
   <si>
+    <t>A3RK</t>
+  </si>
+  <si>
+    <t>A41Z</t>
+  </si>
+  <si>
+    <t>A0IQ</t>
+  </si>
+  <si>
+    <t>D259</t>
+  </si>
+  <si>
+    <t>A3IY</t>
+  </si>
+  <si>
+    <t>A2ID</t>
+  </si>
+  <si>
+    <t>A11F</t>
+  </si>
+  <si>
     <t>A3RO</t>
   </si>
   <si>
-    <t>A41Z</t>
-  </si>
-  <si>
-    <t>A3RK</t>
-  </si>
-  <si>
-    <t>D259</t>
-  </si>
-  <si>
-    <t>A3IY</t>
-  </si>
-  <si>
-    <t>A44H</t>
-  </si>
-  <si>
-    <t>A2IE</t>
-  </si>
-  <si>
-    <t>A30J</t>
-  </si>
-  <si>
-    <t>A2ID</t>
-  </si>
-  <si>
     <t>A2I3</t>
   </si>
   <si>
-    <t>A44G</t>
-  </si>
-  <si>
-    <t>A11F</t>
-  </si>
-  <si>
-    <t>A0IQ</t>
-  </si>
-  <si>
     <t>C216</t>
   </si>
   <si>
+    <t>A3KA</t>
+  </si>
+  <si>
     <t>A2LG</t>
   </si>
   <si>
-    <t>A3KA</t>
-  </si>
-  <si>
     <t>B622</t>
   </si>
   <si>
@@ -346,121 +346,124 @@
     <t>G605</t>
   </si>
   <si>
+    <t>A515</t>
+  </si>
+  <si>
+    <t>A3YJ</t>
+  </si>
+  <si>
+    <t>E794</t>
+  </si>
+  <si>
+    <t>A3NK</t>
+  </si>
+  <si>
+    <t>I588</t>
+  </si>
+  <si>
     <t>A0GK</t>
   </si>
   <si>
-    <t>E794</t>
-  </si>
-  <si>
-    <t>A3NK</t>
-  </si>
-  <si>
-    <t>I588</t>
-  </si>
-  <si>
-    <t>A3YJ</t>
-  </si>
-  <si>
-    <t>A515</t>
+    <t>A2K2</t>
+  </si>
+  <si>
+    <t>A3YI</t>
   </si>
   <si>
     <t>A41F</t>
   </si>
   <si>
-    <t>A2K2</t>
-  </si>
-  <si>
     <t>A3JQ</t>
   </si>
   <si>
-    <t>A3YI</t>
+    <t>A3I6</t>
+  </si>
+  <si>
+    <t>A0GZ</t>
+  </si>
+  <si>
+    <t>A45O</t>
+  </si>
+  <si>
+    <t>A0GT</t>
+  </si>
+  <si>
+    <t>A0GJ</t>
+  </si>
+  <si>
+    <t>A3UE</t>
+  </si>
+  <si>
+    <t>H636</t>
+  </si>
+  <si>
+    <t>C926</t>
+  </si>
+  <si>
+    <t>F766</t>
+  </si>
+  <si>
+    <t>A3ZB</t>
+  </si>
+  <si>
+    <t>A3TV</t>
+  </si>
+  <si>
+    <t>A3Z9</t>
+  </si>
+  <si>
+    <t>A3TS</t>
+  </si>
+  <si>
+    <t>A3JL</t>
+  </si>
+  <si>
+    <t>A4AX</t>
+  </si>
+  <si>
+    <t>A1H9</t>
+  </si>
+  <si>
+    <t>A3WA</t>
+  </si>
+  <si>
+    <t>A3Z0</t>
+  </si>
+  <si>
+    <t>A3YQ</t>
+  </si>
+  <si>
+    <t>A3YK</t>
   </si>
   <si>
     <t>C913</t>
   </si>
   <si>
-    <t>A45O</t>
-  </si>
-  <si>
-    <t>A1H9</t>
-  </si>
-  <si>
-    <t>A0GZ</t>
-  </si>
-  <si>
-    <t>A3JL</t>
-  </si>
-  <si>
-    <t>A3Z9</t>
-  </si>
-  <si>
-    <t>A3TS</t>
-  </si>
-  <si>
-    <t>A4AX</t>
-  </si>
-  <si>
-    <t>A3TV</t>
-  </si>
-  <si>
-    <t>F766</t>
-  </si>
-  <si>
-    <t>H636</t>
-  </si>
-  <si>
-    <t>A0GJ</t>
-  </si>
-  <si>
-    <t>A0GT</t>
-  </si>
-  <si>
-    <t>A3Z0</t>
-  </si>
-  <si>
-    <t>C926</t>
-  </si>
-  <si>
-    <t>A3UE</t>
-  </si>
-  <si>
-    <t>A3WA</t>
-  </si>
-  <si>
-    <t>A3YK</t>
-  </si>
-  <si>
-    <t>A3YQ</t>
-  </si>
-  <si>
     <t>B2UZ</t>
   </si>
   <si>
-    <t>A3ZB</t>
-  </si>
-  <si>
-    <t>A3I6</t>
+    <t>C213</t>
   </si>
   <si>
     <t>A1ZD</t>
   </si>
   <si>
-    <t>C213</t>
+    <t>A3Z2</t>
   </si>
   <si>
     <t>I017</t>
   </si>
   <si>
-    <t>A3Z2</t>
+    <t>A0G7</t>
+  </si>
+  <si>
+    <t>A4DU</t>
   </si>
   <si>
     <t>A3YM</t>
   </si>
   <si>
-    <t>A0G7</t>
-  </si>
-  <si>
-    <t>A4DU</t>
+    <t>H083</t>
   </si>
   <si>
     <t>A2FA</t>
@@ -469,75 +472,75 @@
     <t>A04Q</t>
   </si>
   <si>
-    <t>H083</t>
-  </si>
-  <si>
     <t>A0J5</t>
   </si>
   <si>
+    <t>A3OR</t>
+  </si>
+  <si>
     <t>A4CZ</t>
   </si>
   <si>
-    <t>A3OR</t>
-  </si>
-  <si>
     <t>A194</t>
   </si>
   <si>
+    <t>A2GD</t>
+  </si>
+  <si>
+    <t>A34P</t>
+  </si>
+  <si>
     <t>A2V1</t>
   </si>
   <si>
     <t>A4AF</t>
   </si>
   <si>
+    <t>A37Y</t>
+  </si>
+  <si>
+    <t>A4AL</t>
+  </si>
+  <si>
     <t>A3SV</t>
   </si>
   <si>
-    <t>A4AL</t>
-  </si>
-  <si>
-    <t>A2GD</t>
-  </si>
-  <si>
-    <t>A37Y</t>
-  </si>
-  <si>
-    <t>A34P</t>
+    <t>C947</t>
+  </si>
+  <si>
+    <t>A39M</t>
+  </si>
+  <si>
+    <t>B366</t>
+  </si>
+  <si>
+    <t>A3S7</t>
+  </si>
+  <si>
+    <t>B322</t>
+  </si>
+  <si>
+    <t>A3PS</t>
+  </si>
+  <si>
+    <t>A2FQ</t>
   </si>
   <si>
     <t>A3ON</t>
   </si>
   <si>
-    <t>B322</t>
-  </si>
-  <si>
-    <t>A3PS</t>
-  </si>
-  <si>
-    <t>C947</t>
-  </si>
-  <si>
-    <t>A3S7</t>
-  </si>
-  <si>
-    <t>B366</t>
-  </si>
-  <si>
-    <t>A39M</t>
-  </si>
-  <si>
-    <t>A2FQ</t>
-  </si>
-  <si>
     <t>H146</t>
   </si>
   <si>
+    <t>A3O6</t>
+  </si>
+  <si>
+    <t>G531</t>
+  </si>
+  <si>
     <t>A0IJ</t>
   </si>
   <si>
-    <t>A3O6</t>
-  </si>
-  <si>
     <t>H094</t>
   </si>
   <si>
@@ -547,6 +550,9 @@
     <t>A415</t>
   </si>
   <si>
+    <t>J280</t>
+  </si>
+  <si>
     <t>A2ST</t>
   </si>
   <si>
@@ -556,10 +562,10 @@
     <t>A3DQ</t>
   </si>
   <si>
+    <t>D575</t>
+  </si>
+  <si>
     <t>A3MB</t>
-  </si>
-  <si>
-    <t>D575</t>
   </si>
   <si>
     <t>start_punchtime</t>
@@ -1117,7 +1123,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J215"/>
+  <dimension ref="A1:J217"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.7109375" customWidth="1"/>
@@ -1136,31 +1142,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -1168,21 +1174,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>46028.32740740741</v>
+        <v>46028.679375</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="D2" s="2">
-        <v>46028.70332175926</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>188</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
       <c r="F2" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G2" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="G2" s="2">
+        <v>18.35</v>
+      </c>
       <c r="H2" s="2">
         <v>0</v>
       </c>
@@ -1190,7 +1194,7 @@
         <v>0</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -1198,21 +1202,23 @@
         <v>2</v>
       </c>
       <c r="B3" s="2">
-        <v>46028.2875</v>
+        <v>46028.33421296296</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D3" s="2">
-        <v>46028.73964120371</v>
+        <v>46028.70365740741</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G3" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="G3" s="2">
+        <v>19.6</v>
+      </c>
       <c r="H3" s="2">
         <v>0</v>
       </c>
@@ -1220,7 +1226,7 @@
         <v>0</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1228,21 +1234,23 @@
         <v>3</v>
       </c>
       <c r="B4" s="2">
-        <v>46028.33421296296</v>
+        <v>46028.33333333334</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D4" s="2">
-        <v>46028.70365740741</v>
+        <v>46028.69356481481</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G4" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="G4" s="2">
+        <v>18.7</v>
+      </c>
       <c r="H4" s="2">
         <v>0</v>
       </c>
@@ -1250,7 +1258,7 @@
         <v>0</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1261,18 +1269,20 @@
         <v>46028.33333333334</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D5" s="2">
-        <v>46028.69356481481</v>
+        <v>46028.68002314815</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G5" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="G5" s="2">
+        <v>18.6</v>
+      </c>
       <c r="H5" s="2">
         <v>0</v>
       </c>
@@ -1280,7 +1290,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1288,21 +1298,23 @@
         <v>5</v>
       </c>
       <c r="B6" s="2">
-        <v>46028.33333333334</v>
+        <v>46028.34149305556</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D6" s="2">
-        <v>46028.68002314815</v>
+        <v>46028.69769675926</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G6" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="G6" s="2">
+        <v>18.6</v>
+      </c>
       <c r="H6" s="2">
         <v>0</v>
       </c>
@@ -1310,7 +1322,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1318,21 +1330,23 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>46028.32532407407</v>
+        <v>46028.32763888889</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D7" s="2">
-        <v>46028.7040162037</v>
+        <v>46028.69077546296</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G7" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="G7" s="2">
+        <v>18.35</v>
+      </c>
       <c r="H7" s="2">
         <v>0</v>
       </c>
@@ -1340,7 +1354,7 @@
         <v>0</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1348,21 +1362,23 @@
         <v>7</v>
       </c>
       <c r="B8" s="2">
-        <v>46028.33023148148</v>
+        <v>46028.2875</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D8" s="2">
-        <v>46028.68252314815</v>
+        <v>46028.73964120371</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G8" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="G8" s="2">
+        <v>23</v>
+      </c>
       <c r="H8" s="2">
         <v>0</v>
       </c>
@@ -1370,7 +1386,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1378,21 +1394,23 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>46028.28736111111</v>
+        <v>46028.32532407407</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D9" s="2">
-        <v>46028.71040509259</v>
+        <v>46028.7040162037</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G9" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="G9" s="2">
+        <v>19.6</v>
+      </c>
       <c r="H9" s="2">
         <v>0</v>
       </c>
@@ -1400,7 +1418,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1408,21 +1426,23 @@
         <v>9</v>
       </c>
       <c r="B10" s="2">
-        <v>46028.32782407408</v>
+        <v>46028.32740740741</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D10" s="2">
-        <v>46028.69155092593</v>
+        <v>46028.70332175926</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G10" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="G10" s="2">
+        <v>18.35</v>
+      </c>
       <c r="H10" s="2">
         <v>0</v>
       </c>
@@ -1430,7 +1450,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1438,21 +1458,23 @@
         <v>10</v>
       </c>
       <c r="B11" s="2">
-        <v>46028.32329861111</v>
+        <v>46028.32782407408</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D11" s="2">
-        <v>46028.70388888889</v>
+        <v>46028.69155092593</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G11" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="G11" s="2">
+        <v>18.35</v>
+      </c>
       <c r="H11" s="2">
         <v>0</v>
       </c>
@@ -1460,7 +1482,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1468,21 +1490,23 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>46028.33111111111</v>
+        <v>46028.32329861111</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D12" s="2">
-        <v>46028.69350694444</v>
+        <v>46028.70388888889</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G12" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="G12" s="2">
+        <v>18.7</v>
+      </c>
       <c r="H12" s="2">
         <v>0</v>
       </c>
@@ -1490,7 +1514,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1498,29 +1522,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>46028.33333333334</v>
+        <v>46028.32920138889</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D13" s="2">
-        <v>46028.33333333334</v>
+        <v>46028.68753472222</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G13" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="G13" s="2">
+        <v>18.35</v>
+      </c>
       <c r="H13" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I13" s="2">
         <v>0</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -1528,17 +1554,23 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>46028.33333333334</v>
+        <v>46028.32684027778</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
+        <v>186</v>
+      </c>
+      <c r="D14" s="2">
+        <v>46028.69226851852</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>190</v>
+      </c>
       <c r="F14" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G14" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="G14" s="2">
+        <v>19.6</v>
+      </c>
       <c r="H14" s="2">
         <v>0</v>
       </c>
@@ -1546,25 +1578,31 @@
         <v>0</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" s="2">
-        <v>46028.70609953703</v>
+        <v>46028.33034722223</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
+        <v>186</v>
+      </c>
+      <c r="D15" s="2">
+        <v>46028.70424768519</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>190</v>
+      </c>
       <c r="F15" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G15" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="G15" s="2">
+        <v>18.7</v>
+      </c>
       <c r="H15" s="2">
         <v>0</v>
       </c>
@@ -1572,29 +1610,31 @@
         <v>0</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" s="2">
-        <v>46028.32920138889</v>
+        <v>46028.32734953704</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D16" s="2">
-        <v>46028.68753472222</v>
+        <v>46028.69237268518</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G16" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="G16" s="2">
+        <v>18.7</v>
+      </c>
       <c r="H16" s="2">
         <v>0</v>
       </c>
@@ -1602,29 +1642,31 @@
         <v>0</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17" s="2">
-        <v>46028.32763888889</v>
+        <v>46028.28736111111</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D17" s="2">
-        <v>46028.69077546296</v>
+        <v>46028.71040509259</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G17" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="G17" s="2">
+        <v>26.8</v>
+      </c>
       <c r="H17" s="2">
         <v>0</v>
       </c>
@@ -1632,29 +1674,31 @@
         <v>0</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18" s="2">
-        <v>46028.32684027778</v>
+        <v>46028.32923611111</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D18" s="2">
-        <v>46028.69226851852</v>
+        <v>46028.69554398148</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G18" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="G18" s="2">
+        <v>18.6</v>
+      </c>
       <c r="H18" s="2">
         <v>0</v>
       </c>
@@ -1662,29 +1706,31 @@
         <v>0</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19" s="2">
-        <v>46028.32734953704</v>
+        <v>46028.32494212963</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D19" s="2">
-        <v>46028.69237268518</v>
+        <v>46028.6875</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G19" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="G19" s="2">
+        <v>18.35</v>
+      </c>
       <c r="H19" s="2">
         <v>0</v>
       </c>
@@ -1692,29 +1738,31 @@
         <v>0</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20" s="2">
-        <v>46028.32923611111</v>
+        <v>46028.32569444444</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D20" s="2">
-        <v>46028.69554398148</v>
+        <v>46028.70412037037</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G20" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="G20" s="2">
+        <v>18.7</v>
+      </c>
       <c r="H20" s="2">
         <v>0</v>
       </c>
@@ -1722,29 +1770,31 @@
         <v>0</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" s="2">
-        <v>46028.33333333334</v>
+        <v>46028.33111111111</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D21" s="2">
-        <v>46028.70871527777</v>
+        <v>46028.69350694444</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G21" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="G21" s="2">
+        <v>18.7</v>
+      </c>
       <c r="H21" s="2">
         <v>0</v>
       </c>
@@ -1752,59 +1802,59 @@
         <v>0</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22" s="2">
-        <v>46028.32494212963</v>
+        <v>46028.33333333334</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D22" s="2">
-        <v>46028.6875</v>
+        <v>46028.33333333334</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G22" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="G22" s="2">
+        <v>18.7</v>
+      </c>
       <c r="H22" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I22" s="2">
         <v>0</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B23" s="2">
-        <v>46028.33142361111</v>
+        <v>46028.33333333334</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="D23" s="2">
-        <v>46028.70585648148</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>188</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
       <c r="F23" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G23" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="G23" s="2">
+        <v>18.7</v>
+      </c>
       <c r="H23" s="2">
         <v>0</v>
       </c>
@@ -1812,7 +1862,7 @@
         <v>0</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -1820,21 +1870,19 @@
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>46028.32841435185</v>
+        <v>46028.70609953703</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="D24" s="2">
-        <v>46028.68475694444</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>188</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
       <c r="F24" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G24" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="G24" s="2">
+        <v>18.7</v>
+      </c>
       <c r="H24" s="2">
         <v>0</v>
       </c>
@@ -1842,7 +1890,7 @@
         <v>0</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -1850,21 +1898,23 @@
         <v>23</v>
       </c>
       <c r="B25" s="2">
-        <v>46028.34805555556</v>
+        <v>46028.33142361111</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D25" s="2">
-        <v>46028.67934027778</v>
+        <v>46028.70585648148</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G25" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="G25" s="2">
+        <v>18.35</v>
+      </c>
       <c r="H25" s="2">
         <v>0</v>
       </c>
@@ -1872,25 +1922,31 @@
         <v>0</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B26" s="2">
-        <v>46028.679375</v>
+        <v>46028.32841435185</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
+        <v>186</v>
+      </c>
+      <c r="D26" s="2">
+        <v>46028.68475694444</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>190</v>
+      </c>
       <c r="F26" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G26" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="G26" s="2">
+        <v>18.35</v>
+      </c>
       <c r="H26" s="2">
         <v>0</v>
       </c>
@@ -1898,29 +1954,31 @@
         <v>0</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="B27" s="2">
-        <v>46028.33030092593</v>
+        <v>46028.34805555556</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D27" s="2">
-        <v>46028.36953703704</v>
+        <v>46028.67934027778</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G27" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="G27" s="2">
+        <v>18.35</v>
+      </c>
       <c r="H27" s="2">
         <v>0</v>
       </c>
@@ -1928,7 +1986,7 @@
         <v>0</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -1936,21 +1994,23 @@
         <v>25</v>
       </c>
       <c r="B28" s="2">
-        <v>46028.33046296296</v>
+        <v>46028.33030092593</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D28" s="2">
-        <v>46028.70054398148</v>
+        <v>46028.36953703704</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G28" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="G28" s="2">
+        <v>18.35</v>
+      </c>
       <c r="H28" s="2">
         <v>0</v>
       </c>
@@ -1958,7 +2018,7 @@
         <v>0</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -1966,21 +2026,23 @@
         <v>26</v>
       </c>
       <c r="B29" s="2">
-        <v>46028.32789351852</v>
+        <v>46028.33046296296</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D29" s="2">
-        <v>46028.69924768519</v>
+        <v>46028.70054398148</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G29" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="G29" s="2">
+        <v>18.7</v>
+      </c>
       <c r="H29" s="2">
         <v>0</v>
       </c>
@@ -1988,7 +2050,7 @@
         <v>0</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -1996,21 +2058,23 @@
         <v>27</v>
       </c>
       <c r="B30" s="2">
-        <v>46028.32333333333</v>
+        <v>46028.32789351852</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D30" s="2">
-        <v>46028.68923611111</v>
+        <v>46028.69924768519</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G30" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="G30" s="2">
+        <v>19.6</v>
+      </c>
       <c r="H30" s="2">
         <v>0</v>
       </c>
@@ -2018,7 +2082,7 @@
         <v>0</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -2026,21 +2090,23 @@
         <v>28</v>
       </c>
       <c r="B31" s="2">
-        <v>46028.32569444444</v>
+        <v>46028.32333333333</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D31" s="2">
-        <v>46028.70412037037</v>
+        <v>46028.68923611111</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G31" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="G31" s="2">
+        <v>18.35</v>
+      </c>
       <c r="H31" s="2">
         <v>0</v>
       </c>
@@ -2048,7 +2114,7 @@
         <v>0</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -2059,18 +2125,20 @@
         <v>46028.32296296296</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D32" s="2">
         <v>46028.68834490741</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G32" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="G32" s="2">
+        <v>19.6</v>
+      </c>
       <c r="H32" s="2">
         <v>0</v>
       </c>
@@ -2078,7 +2146,7 @@
         <v>0</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -2086,21 +2154,23 @@
         <v>30</v>
       </c>
       <c r="B33" s="2">
-        <v>46028.33034722223</v>
+        <v>46028.33333333334</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D33" s="2">
-        <v>46028.70424768519</v>
+        <v>46028.70871527777</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G33" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="G33" s="2">
+        <v>18.6</v>
+      </c>
       <c r="H33" s="2">
         <v>0</v>
       </c>
@@ -2108,7 +2178,7 @@
         <v>0</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -2116,21 +2186,23 @@
         <v>31</v>
       </c>
       <c r="B34" s="2">
-        <v>46028.34149305556</v>
+        <v>46028.33023148148</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D34" s="2">
-        <v>46028.69769675926</v>
+        <v>46028.68252314815</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G34" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="G34" s="2">
+        <v>18.35</v>
+      </c>
       <c r="H34" s="2">
         <v>0</v>
       </c>
@@ -2138,7 +2210,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -2149,18 +2221,20 @@
         <v>46028.27280092592</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D35" s="2">
         <v>46028.71306712963</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="G35" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="G35" s="2">
+        <v>27</v>
+      </c>
       <c r="H35" s="2">
         <v>0</v>
       </c>
@@ -2168,7 +2242,7 @@
         <v>0</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -2179,18 +2253,20 @@
         <v>46028.26738425926</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D36" s="2">
         <v>46028.71222222222</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="G36" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="G36" s="2">
+        <v>20.2</v>
+      </c>
       <c r="H36" s="2">
         <v>0</v>
       </c>
@@ -2198,7 +2274,7 @@
         <v>0</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -2209,18 +2285,20 @@
         <v>46028.2691087963</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D37" s="2">
         <v>46028.71334490741</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="G37" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="G37" s="2">
+        <v>22.4</v>
+      </c>
       <c r="H37" s="2">
         <v>0</v>
       </c>
@@ -2228,7 +2306,7 @@
         <v>0</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -2236,21 +2314,23 @@
         <v>35</v>
       </c>
       <c r="B38" s="2">
-        <v>46028.5824537037</v>
+        <v>46028.30696759259</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D38" s="2">
-        <v>46029.00518518518</v>
+        <v>46028.73030092593</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="G38" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="G38" s="2">
+        <v>30.75</v>
+      </c>
       <c r="H38" s="2">
         <v>0</v>
       </c>
@@ -2258,7 +2338,7 @@
         <v>0</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -2269,18 +2349,20 @@
         <v>46028.49609953703</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D39" s="2">
         <v>46029.0171412037</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="G39" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="G39" s="2">
+        <v>23</v>
+      </c>
       <c r="H39" s="2">
         <v>0</v>
       </c>
@@ -2288,7 +2370,7 @@
         <v>0</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="40" spans="1:10">
@@ -2299,14 +2381,20 @@
         <v>46028.99396990741</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
+        <v>186</v>
+      </c>
+      <c r="D40" s="2">
+        <v>46029.50740740741</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>190</v>
+      </c>
       <c r="F40" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="G40" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="G40" s="2">
+        <v>20.2</v>
+      </c>
       <c r="H40" s="2">
         <v>0</v>
       </c>
@@ -2314,7 +2402,7 @@
         <v>0</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="41" spans="1:10">
@@ -2325,16 +2413,16 @@
         <v>46028.01143518519</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D41" s="2">
         <v>46028.32390046296</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G41" s="2">
         <v>19.65</v>
@@ -2346,7 +2434,7 @@
         <v>0</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="42" spans="1:10">
@@ -2354,17 +2442,23 @@
         <v>39</v>
       </c>
       <c r="B42" s="2">
-        <v>46028.99173611111</v>
+        <v>46028.57844907408</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
+        <v>186</v>
+      </c>
+      <c r="D42" s="2">
+        <v>46029.00565972222</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>190</v>
+      </c>
       <c r="F42" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="G42" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="G42" s="2">
+        <v>20.2</v>
+      </c>
       <c r="H42" s="2">
         <v>0</v>
       </c>
@@ -2372,7 +2466,7 @@
         <v>0</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="43" spans="1:10">
@@ -2380,17 +2474,23 @@
         <v>40</v>
       </c>
       <c r="B43" s="2">
-        <v>46028.99106481481</v>
+        <v>46028.50171296296</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
+        <v>186</v>
+      </c>
+      <c r="D43" s="2">
+        <v>46029.00728009259</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>190</v>
+      </c>
       <c r="F43" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="G43" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="G43" s="2">
+        <v>23</v>
+      </c>
       <c r="H43" s="2">
         <v>0</v>
       </c>
@@ -2398,7 +2498,7 @@
         <v>0</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="44" spans="1:10">
@@ -2406,21 +2506,23 @@
         <v>41</v>
       </c>
       <c r="B44" s="2">
-        <v>46028.49564814815</v>
+        <v>46028.5750462963</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D44" s="2">
-        <v>46029.01710648148</v>
+        <v>46029.00039351852</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="G44" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="G44" s="2">
+        <v>20.2</v>
+      </c>
       <c r="H44" s="2">
         <v>0</v>
       </c>
@@ -2428,7 +2530,7 @@
         <v>0</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="45" spans="1:10">
@@ -2436,21 +2538,23 @@
         <v>42</v>
       </c>
       <c r="B45" s="2">
-        <v>46028.50171296296</v>
+        <v>46028.49564814815</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D45" s="2">
-        <v>46029.00728009259</v>
+        <v>46029.01710648148</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="G45" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="G45" s="2">
+        <v>22.4</v>
+      </c>
       <c r="H45" s="2">
         <v>0</v>
       </c>
@@ -2458,7 +2562,7 @@
         <v>0</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="46" spans="1:10">
@@ -2466,21 +2570,19 @@
         <v>43</v>
       </c>
       <c r="B46" s="2">
-        <v>46028.5750462963</v>
+        <v>46028.99106481481</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="D46" s="2">
-        <v>46029.00039351852</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>188</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
       <c r="F46" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="G46" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="G46" s="2">
+        <v>20.2</v>
+      </c>
       <c r="H46" s="2">
         <v>0</v>
       </c>
@@ -2488,7 +2590,7 @@
         <v>0</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="47" spans="1:10">
@@ -2496,21 +2598,23 @@
         <v>44</v>
       </c>
       <c r="B47" s="2">
-        <v>46028.30696759259</v>
+        <v>46028.99173611111</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D47" s="2">
-        <v>46028.73030092593</v>
+        <v>46029.56185185185</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="G47" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="G47" s="2">
+        <v>20.2</v>
+      </c>
       <c r="H47" s="2">
         <v>0</v>
       </c>
@@ -2518,7 +2622,7 @@
         <v>0</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="48" spans="1:10">
@@ -2526,21 +2630,23 @@
         <v>45</v>
       </c>
       <c r="B48" s="2">
-        <v>46028.57844907408</v>
+        <v>46028.5824537037</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D48" s="2">
-        <v>46029.00565972222</v>
+        <v>46029.00518518518</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="G48" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="G48" s="2">
+        <v>20.2</v>
+      </c>
       <c r="H48" s="2">
         <v>0</v>
       </c>
@@ -2548,7 +2654,7 @@
         <v>0</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="49" spans="1:10">
@@ -2559,18 +2665,20 @@
         <v>46028.30431712963</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D49" s="2">
         <v>46028.75038194445</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="G49" s="2"/>
+        <v>195</v>
+      </c>
+      <c r="G49" s="2">
+        <v>18.35</v>
+      </c>
       <c r="H49" s="2">
         <v>0</v>
       </c>
@@ -2578,7 +2686,7 @@
         <v>0</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="50" spans="1:10">
@@ -2589,18 +2697,20 @@
         <v>46028.30416666667</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D50" s="2">
         <v>46028.75038194445</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="G50" s="2"/>
+        <v>195</v>
+      </c>
+      <c r="G50" s="2">
+        <v>18.35</v>
+      </c>
       <c r="H50" s="2">
         <v>0</v>
       </c>
@@ -2608,7 +2718,7 @@
         <v>0</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="51" spans="1:10">
@@ -2619,18 +2729,20 @@
         <v>46028.31930555555</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D51" s="2">
         <v>46028.73261574074</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="G51" s="2"/>
+        <v>195</v>
+      </c>
+      <c r="G51" s="2">
+        <v>24</v>
+      </c>
       <c r="H51" s="2">
         <v>0</v>
       </c>
@@ -2638,7 +2750,7 @@
         <v>0</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="52" spans="1:10">
@@ -2646,21 +2758,23 @@
         <v>48</v>
       </c>
       <c r="B52" s="2">
-        <v>46028.69006944444</v>
+        <v>46028.90832175926</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D52" s="2">
-        <v>46028.92</v>
+        <v>46029.39414351852</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="G52" s="2"/>
+        <v>196</v>
+      </c>
+      <c r="G52" s="2">
+        <v>22.4</v>
+      </c>
       <c r="H52" s="2">
         <v>0</v>
       </c>
@@ -2668,7 +2782,7 @@
         <v>0</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="53" spans="1:10">
@@ -2676,21 +2790,23 @@
         <v>49</v>
       </c>
       <c r="B53" s="2">
-        <v>46028.08225694444</v>
+        <v>46028.68292824074</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D53" s="2">
-        <v>46028.40329861111</v>
+        <v>46029.08340277777</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="G53" s="2"/>
+        <v>196</v>
+      </c>
+      <c r="G53" s="2">
+        <v>29.25</v>
+      </c>
       <c r="H53" s="2">
         <v>0</v>
       </c>
@@ -2698,29 +2814,31 @@
         <v>0</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="54" spans="1:10">
       <c r="A54" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B54" s="2">
         <v>46028.07134259259</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D54" s="2">
         <v>46028.41072916667</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="G54" s="2"/>
+        <v>196</v>
+      </c>
+      <c r="G54" s="2">
+        <v>22.4</v>
+      </c>
       <c r="H54" s="2">
         <v>0</v>
       </c>
@@ -2728,7 +2846,7 @@
         <v>0</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="55" spans="1:10">
@@ -2736,17 +2854,23 @@
         <v>50</v>
       </c>
       <c r="B55" s="2">
-        <v>46028.90832175926</v>
+        <v>46028.08225694444</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="D55" s="2"/>
-      <c r="E55" s="2"/>
+        <v>186</v>
+      </c>
+      <c r="D55" s="2">
+        <v>46028.40329861111</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>190</v>
+      </c>
       <c r="F55" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="G55" s="2"/>
+        <v>196</v>
+      </c>
+      <c r="G55" s="2">
+        <v>20.7</v>
+      </c>
       <c r="H55" s="2">
         <v>0</v>
       </c>
@@ -2754,7 +2878,7 @@
         <v>0</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="56" spans="1:10">
@@ -2762,21 +2886,23 @@
         <v>51</v>
       </c>
       <c r="B56" s="2">
-        <v>46028.68292824074</v>
+        <v>46028.69006944444</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D56" s="2">
-        <v>46029.08340277777</v>
+        <v>46028.92</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="G56" s="2"/>
+        <v>196</v>
+      </c>
+      <c r="G56" s="2">
+        <v>23</v>
+      </c>
       <c r="H56" s="2">
         <v>0</v>
       </c>
@@ -2784,7 +2910,7 @@
         <v>0</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="57" spans="1:10">
@@ -2795,18 +2921,20 @@
         <v>46028.52333333333</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D57" s="2">
         <v>46029.29164351852</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="G57" s="2"/>
+        <v>197</v>
+      </c>
+      <c r="G57" s="2">
+        <v>35.5</v>
+      </c>
       <c r="H57" s="2">
         <v>0</v>
       </c>
@@ -2814,29 +2942,31 @@
         <v>0</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="58" spans="1:10">
       <c r="A58" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B58" s="2">
-        <v>46028.38378472222</v>
+        <v>46028.29003472222</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D58" s="2">
-        <v>46028.73631944445</v>
+        <v>46028.50280092593</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="G58" s="2"/>
+        <v>197</v>
+      </c>
+      <c r="G58" s="2">
+        <v>35.5</v>
+      </c>
       <c r="H58" s="2">
         <v>0</v>
       </c>
@@ -2844,29 +2974,31 @@
         <v>0</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="59" spans="1:10">
       <c r="A59" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B59" s="2">
-        <v>46028.29003472222</v>
+        <v>46028.38378472222</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D59" s="2">
-        <v>46028.50280092593</v>
+        <v>46028.73631944445</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="G59" s="2"/>
+        <v>197</v>
+      </c>
+      <c r="G59" s="2">
+        <v>40.5</v>
+      </c>
       <c r="H59" s="2">
         <v>0</v>
       </c>
@@ -2874,7 +3006,7 @@
         <v>0</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="60" spans="1:10">
@@ -2882,21 +3014,23 @@
         <v>54</v>
       </c>
       <c r="B60" s="2">
-        <v>46028.32686342593</v>
+        <v>46028.31663194444</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D60" s="2">
-        <v>46028.71752314815</v>
+        <v>46028.72543981481</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="G60" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="G60" s="2">
+        <v>23.85</v>
+      </c>
       <c r="H60" s="2">
         <v>0</v>
       </c>
@@ -2904,7 +3038,7 @@
         <v>0</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="61" spans="1:10">
@@ -2912,21 +3046,23 @@
         <v>55</v>
       </c>
       <c r="B61" s="2">
-        <v>46028.31143518518</v>
+        <v>46028.32635416667</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D61" s="2">
-        <v>46028.72353009259</v>
+        <v>46028.71736111111</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="G61" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="G61" s="2">
+        <v>22.4</v>
+      </c>
       <c r="H61" s="2">
         <v>0</v>
       </c>
@@ -2934,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="62" spans="1:10">
@@ -2942,21 +3078,23 @@
         <v>56</v>
       </c>
       <c r="B62" s="2">
-        <v>46028.32162037037</v>
+        <v>46028.33210648148</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D62" s="2">
-        <v>46028.7137037037</v>
+        <v>46028.71081018518</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="G62" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="G62" s="2">
+        <v>22.4</v>
+      </c>
       <c r="H62" s="2">
         <v>0</v>
       </c>
@@ -2964,7 +3102,7 @@
         <v>0</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="63" spans="1:10">
@@ -2972,21 +3110,23 @@
         <v>57</v>
       </c>
       <c r="B63" s="2">
-        <v>46028.32329861111</v>
+        <v>46028.32435185185</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D63" s="2">
-        <v>46028.7277662037</v>
+        <v>46028.71934027778</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="G63" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="G63" s="2">
+        <v>20.2</v>
+      </c>
       <c r="H63" s="2">
         <v>0</v>
       </c>
@@ -2994,7 +3134,7 @@
         <v>0</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="64" spans="1:10">
@@ -3002,21 +3142,23 @@
         <v>58</v>
       </c>
       <c r="B64" s="2">
-        <v>46028.32077546296</v>
+        <v>46028.32484953704</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D64" s="2">
-        <v>46028.72177083333</v>
+        <v>46028.72642361111</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="G64" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="G64" s="2">
+        <v>23</v>
+      </c>
       <c r="H64" s="2">
         <v>0</v>
       </c>
@@ -3024,7 +3166,7 @@
         <v>0</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="65" spans="1:10">
@@ -3032,21 +3174,23 @@
         <v>59</v>
       </c>
       <c r="B65" s="2">
-        <v>46028.31663194444</v>
+        <v>46028.31960648148</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D65" s="2">
-        <v>46028.72543981481</v>
+        <v>46028.72921296296</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="G65" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="G65" s="2">
+        <v>20.95</v>
+      </c>
       <c r="H65" s="2">
         <v>0</v>
       </c>
@@ -3054,7 +3198,7 @@
         <v>0</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="66" spans="1:10">
@@ -3062,21 +3206,23 @@
         <v>60</v>
       </c>
       <c r="B66" s="2">
-        <v>46028.32435185185</v>
+        <v>46028.31273148148</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D66" s="2">
-        <v>46028.71934027778</v>
+        <v>46028.7300462963</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="G66" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="G66" s="2">
+        <v>22.4</v>
+      </c>
       <c r="H66" s="2">
         <v>0</v>
       </c>
@@ -3084,7 +3230,7 @@
         <v>0</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="67" spans="1:10">
@@ -3095,18 +3241,20 @@
         <v>46028.31771990741</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D67" s="2">
         <v>46028.73119212963</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="G67" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="G67" s="2">
+        <v>23.35</v>
+      </c>
       <c r="H67" s="2">
         <v>0</v>
       </c>
@@ -3114,7 +3262,7 @@
         <v>0</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="68" spans="1:10">
@@ -3122,21 +3270,23 @@
         <v>62</v>
       </c>
       <c r="B68" s="2">
-        <v>46028.32635416667</v>
+        <v>46028.31143518518</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D68" s="2">
-        <v>46028.71736111111</v>
+        <v>46028.72353009259</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="G68" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="G68" s="2">
+        <v>24.8</v>
+      </c>
       <c r="H68" s="2">
         <v>0</v>
       </c>
@@ -3144,7 +3294,7 @@
         <v>0</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="69" spans="1:10">
@@ -3152,21 +3302,23 @@
         <v>63</v>
       </c>
       <c r="B69" s="2">
-        <v>46028.33210648148</v>
+        <v>46028.3160300926</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D69" s="2">
-        <v>46028.71081018518</v>
+        <v>46028.72043981482</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="G69" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="G69" s="2">
+        <v>20.2</v>
+      </c>
       <c r="H69" s="2">
         <v>0</v>
       </c>
@@ -3174,7 +3326,7 @@
         <v>0</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="70" spans="1:10">
@@ -3182,21 +3334,23 @@
         <v>64</v>
       </c>
       <c r="B70" s="2">
-        <v>46028.31655092593</v>
+        <v>46028.32077546296</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D70" s="2">
-        <v>46028.72543981481</v>
+        <v>46028.72177083333</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="G70" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="G70" s="2">
+        <v>23.85</v>
+      </c>
       <c r="H70" s="2">
         <v>0</v>
       </c>
@@ -3204,7 +3358,7 @@
         <v>0</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="71" spans="1:10">
@@ -3212,21 +3366,23 @@
         <v>65</v>
       </c>
       <c r="B71" s="2">
-        <v>46028.32484953704</v>
+        <v>46028.31655092593</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D71" s="2">
-        <v>46028.72642361111</v>
+        <v>46028.72543981481</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="G71" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="G71" s="2">
+        <v>22.4</v>
+      </c>
       <c r="H71" s="2">
         <v>0</v>
       </c>
@@ -3234,7 +3390,7 @@
         <v>0</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="72" spans="1:10">
@@ -3242,21 +3398,23 @@
         <v>66</v>
       </c>
       <c r="B72" s="2">
-        <v>46028.31960648148</v>
+        <v>46028.32329861111</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D72" s="2">
-        <v>46028.72921296296</v>
+        <v>46028.7277662037</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="G72" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="G72" s="2">
+        <v>20.7</v>
+      </c>
       <c r="H72" s="2">
         <v>0</v>
       </c>
@@ -3264,7 +3422,7 @@
         <v>0</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="73" spans="1:10">
@@ -3272,21 +3430,23 @@
         <v>67</v>
       </c>
       <c r="B73" s="2">
-        <v>46028.31273148148</v>
+        <v>46028.32686342593</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D73" s="2">
-        <v>46028.7300462963</v>
+        <v>46028.71752314815</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="G73" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="G73" s="2">
+        <v>19.25</v>
+      </c>
       <c r="H73" s="2">
         <v>0</v>
       </c>
@@ -3294,7 +3454,7 @@
         <v>0</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="74" spans="1:10">
@@ -3302,21 +3462,23 @@
         <v>68</v>
       </c>
       <c r="B74" s="2">
-        <v>46028.31408564815</v>
+        <v>46028.32162037037</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D74" s="2">
-        <v>46028.72826388889</v>
+        <v>46028.7137037037</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="G74" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="G74" s="2">
+        <v>20.95</v>
+      </c>
       <c r="H74" s="2">
         <v>0</v>
       </c>
@@ -3324,7 +3486,7 @@
         <v>0</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="75" spans="1:10">
@@ -3332,21 +3494,23 @@
         <v>69</v>
       </c>
       <c r="B75" s="2">
-        <v>46028.3160300926</v>
+        <v>46028.31408564815</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D75" s="2">
-        <v>46028.72043981482</v>
+        <v>46028.72826388889</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="G75" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="G75" s="2">
+        <v>23.85</v>
+      </c>
       <c r="H75" s="2">
         <v>0</v>
       </c>
@@ -3354,7 +3518,7 @@
         <v>0</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="76" spans="1:10">
@@ -3362,21 +3526,23 @@
         <v>70</v>
       </c>
       <c r="B76" s="2">
-        <v>46028.32605324074</v>
+        <v>46028.34030092593</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D76" s="2">
-        <v>46028.52202546296</v>
+        <v>46028.64033564815</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="G76" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="G76" s="2">
+        <v>19.6</v>
+      </c>
       <c r="H76" s="2">
         <v>0</v>
       </c>
@@ -3384,7 +3550,7 @@
         <v>0</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="77" spans="1:10">
@@ -3392,21 +3558,23 @@
         <v>71</v>
       </c>
       <c r="B77" s="2">
-        <v>46028.31328703704</v>
+        <v>46028.32212962963</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D77" s="2">
-        <v>46028.48303240741</v>
+        <v>46028.60967592592</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="G77" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="G77" s="2">
+        <v>19.25</v>
+      </c>
       <c r="H77" s="2">
         <v>0</v>
       </c>
@@ -3414,7 +3582,7 @@
         <v>0</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="78" spans="1:10">
@@ -3422,21 +3590,23 @@
         <v>72</v>
       </c>
       <c r="B78" s="2">
-        <v>46028.32201388889</v>
+        <v>46028.32638888889</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D78" s="2">
-        <v>46028.48976851852</v>
+        <v>46028.74807870371</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="G78" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="G78" s="2">
+        <v>22.4</v>
+      </c>
       <c r="H78" s="2">
         <v>0</v>
       </c>
@@ -3444,7 +3614,7 @@
         <v>0</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="79" spans="1:10">
@@ -3452,17 +3622,23 @@
         <v>73</v>
       </c>
       <c r="B79" s="2">
-        <v>46028.40208333333</v>
+        <v>46028.32633101852</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="D79" s="2"/>
-      <c r="E79" s="2"/>
+        <v>186</v>
+      </c>
+      <c r="D79" s="2">
+        <v>46028.579375</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>190</v>
+      </c>
       <c r="F79" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="G79" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="G79" s="2">
+        <v>19.25</v>
+      </c>
       <c r="H79" s="2">
         <v>0</v>
       </c>
@@ -3470,7 +3646,7 @@
         <v>0</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="80" spans="1:10">
@@ -3478,21 +3654,23 @@
         <v>74</v>
       </c>
       <c r="B80" s="2">
-        <v>46028.3235300926</v>
+        <v>46028.32605324074</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D80" s="2">
-        <v>46028.68962962963</v>
+        <v>46028.52202546296</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="G80" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="G80" s="2">
+        <v>19.25</v>
+      </c>
       <c r="H80" s="2">
         <v>0</v>
       </c>
@@ -3500,7 +3678,7 @@
         <v>0</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="81" spans="1:10">
@@ -3511,18 +3689,20 @@
         <v>46028.32541666667</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D81" s="2">
         <v>46028.50273148148</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="G81" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="G81" s="2">
+        <v>19.25</v>
+      </c>
       <c r="H81" s="2">
         <v>0</v>
       </c>
@@ -3530,7 +3710,7 @@
         <v>0</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="82" spans="1:10">
@@ -3541,16 +3721,16 @@
         <v>46028.32877314815</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D82" s="2">
         <v>46028.56314814815</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G82" s="2">
         <v>18.75</v>
@@ -3562,7 +3742,7 @@
         <v>0</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="83" spans="1:10">
@@ -3570,21 +3750,23 @@
         <v>77</v>
       </c>
       <c r="B83" s="2">
-        <v>46028.32212962963</v>
+        <v>46028.31328703704</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D83" s="2">
-        <v>46028.67184027778</v>
+        <v>46028.48303240741</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="G83" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="G83" s="2">
+        <v>19.25</v>
+      </c>
       <c r="H83" s="2">
         <v>0</v>
       </c>
@@ -3592,7 +3774,7 @@
         <v>0</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="84" spans="1:10">
@@ -3600,21 +3782,23 @@
         <v>78</v>
       </c>
       <c r="B84" s="2">
-        <v>46028.32633101852</v>
+        <v>46028.37208333334</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D84" s="2">
-        <v>46028.579375</v>
+        <v>46028.69359953704</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="G84" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="G84" s="2">
+        <v>19.6</v>
+      </c>
       <c r="H84" s="2">
         <v>0</v>
       </c>
@@ -3622,7 +3806,7 @@
         <v>0</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="85" spans="1:10">
@@ -3630,21 +3814,19 @@
         <v>79</v>
       </c>
       <c r="B85" s="2">
-        <v>46028.32638888889</v>
+        <v>46028.40208333333</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="D85" s="2">
-        <v>46028.74807870371</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>188</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="D85" s="2"/>
+      <c r="E85" s="2"/>
       <c r="F85" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="G85" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="G85" s="2">
+        <v>19.75</v>
+      </c>
       <c r="H85" s="2">
         <v>0</v>
       </c>
@@ -3652,29 +3834,27 @@
         <v>0</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" spans="1:10">
       <c r="A86" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B86" s="2">
-        <v>46028.32212962963</v>
+        <v>46028.66666666666</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="D86" s="2">
-        <v>46028.60967592592</v>
-      </c>
-      <c r="E86" s="2" t="s">
-        <v>188</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="D86" s="2"/>
+      <c r="E86" s="2"/>
       <c r="F86" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="G86" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="G86" s="2">
+        <v>19.75</v>
+      </c>
       <c r="H86" s="2">
         <v>0</v>
       </c>
@@ -3682,29 +3862,31 @@
         <v>0</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="87" spans="1:10">
       <c r="A87" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B87" s="2">
-        <v>46028.32482638889</v>
+        <v>46028.32201388889</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D87" s="2">
-        <v>46028.60695601852</v>
+        <v>46028.48976851852</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="G87" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="G87" s="2">
+        <v>19.25</v>
+      </c>
       <c r="H87" s="2">
         <v>0</v>
       </c>
@@ -3712,29 +3894,31 @@
         <v>0</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="88" spans="1:10">
       <c r="A88" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B88" s="2">
-        <v>46028.34030092593</v>
+        <v>46028.32212962963</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D88" s="2">
-        <v>46028.64033564815</v>
+        <v>46028.67184027778</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="G88" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="G88" s="2">
+        <v>19.25</v>
+      </c>
       <c r="H88" s="2">
         <v>0</v>
       </c>
@@ -3742,29 +3926,31 @@
         <v>0</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="89" spans="1:10">
       <c r="A89" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B89" s="2">
-        <v>46028.37208333334</v>
+        <v>46028.3235300926</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D89" s="2">
-        <v>46028.69359953704</v>
+        <v>46028.68962962963</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="G89" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="G89" s="2">
+        <v>19.25</v>
+      </c>
       <c r="H89" s="2">
         <v>0</v>
       </c>
@@ -3772,29 +3958,31 @@
         <v>0</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="90" spans="1:10">
       <c r="A90" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B90" s="2">
-        <v>46028.40625</v>
+        <v>46028.32482638889</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D90" s="2">
-        <v>46028.66666666666</v>
+        <v>46028.60695601852</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="G90" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="G90" s="2">
+        <v>19.6</v>
+      </c>
       <c r="H90" s="2">
         <v>0</v>
       </c>
@@ -3802,25 +3990,31 @@
         <v>0</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="91" spans="1:10">
       <c r="A91" s="2" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="B91" s="2">
+        <v>46028.40625</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D91" s="2">
         <v>46028.66666666666</v>
       </c>
-      <c r="C91" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="D91" s="2"/>
-      <c r="E91" s="2"/>
+      <c r="E91" s="2" t="s">
+        <v>190</v>
+      </c>
       <c r="F91" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="G91" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="G91" s="2">
+        <v>19.75</v>
+      </c>
       <c r="H91" s="2">
         <v>0</v>
       </c>
@@ -3828,7 +4022,7 @@
         <v>0</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="92" spans="1:10">
@@ -3836,21 +4030,23 @@
         <v>85</v>
       </c>
       <c r="B92" s="2">
-        <v>46028.32207175926</v>
+        <v>46028.32240740741</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D92" s="2">
-        <v>46028.58526620371</v>
+        <v>46028.69782407407</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="G92" s="2"/>
+        <v>200</v>
+      </c>
+      <c r="G92" s="2">
+        <v>23</v>
+      </c>
       <c r="H92" s="2">
         <v>0</v>
       </c>
@@ -3858,7 +4054,7 @@
         <v>0</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="93" spans="1:10">
@@ -3866,21 +4062,23 @@
         <v>86</v>
       </c>
       <c r="B93" s="2">
-        <v>46028.41351851852</v>
+        <v>46028.61877314815</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D93" s="2">
-        <v>46028.69342592593</v>
+        <v>46028.61878472222</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="G93" s="2"/>
+        <v>200</v>
+      </c>
+      <c r="G93" s="2">
+        <v>19.6</v>
+      </c>
       <c r="H93" s="2">
         <v>0</v>
       </c>
@@ -3888,7 +4086,7 @@
         <v>0</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="94" spans="1:10">
@@ -3896,21 +4094,23 @@
         <v>87</v>
       </c>
       <c r="B94" s="2">
-        <v>46028.32240740741</v>
+        <v>46028.41351851852</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D94" s="2">
-        <v>46028.69782407407</v>
+        <v>46028.69342592593</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="G94" s="2"/>
+        <v>200</v>
+      </c>
+      <c r="G94" s="2">
+        <v>23.35</v>
+      </c>
       <c r="H94" s="2">
         <v>0</v>
       </c>
@@ -3918,7 +4118,7 @@
         <v>0</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="95" spans="1:10">
@@ -3926,21 +4126,23 @@
         <v>88</v>
       </c>
       <c r="B95" s="2">
-        <v>46028.61877314815</v>
+        <v>46028.32207175926</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D95" s="2">
-        <v>46028.61878472222</v>
+        <v>46028.58526620371</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="G95" s="2"/>
+        <v>200</v>
+      </c>
+      <c r="G95" s="2">
+        <v>23.35</v>
+      </c>
       <c r="H95" s="2">
         <v>0</v>
       </c>
@@ -3948,7 +4150,7 @@
         <v>0</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="96" spans="1:10">
@@ -3956,21 +4158,23 @@
         <v>89</v>
       </c>
       <c r="B96" s="2">
-        <v>46028.31493055556</v>
+        <v>46028.54517361111</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D96" s="2">
-        <v>46028.57921296296</v>
+        <v>46028.72144675926</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="G96" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="G96" s="2">
+        <v>18.6</v>
+      </c>
       <c r="H96" s="2">
         <v>0</v>
       </c>
@@ -3978,7 +4182,7 @@
         <v>0</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="97" spans="1:10">
@@ -3986,21 +4190,23 @@
         <v>90</v>
       </c>
       <c r="B97" s="2">
-        <v>46028.32509259259</v>
+        <v>46028.31493055556</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D97" s="2">
-        <v>46028.58266203704</v>
+        <v>46028.57921296296</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="G97" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="G97" s="2">
+        <v>19.75</v>
+      </c>
       <c r="H97" s="2">
         <v>0</v>
       </c>
@@ -4008,7 +4214,7 @@
         <v>0</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="98" spans="1:10">
@@ -4016,21 +4222,23 @@
         <v>91</v>
       </c>
       <c r="B98" s="2">
-        <v>46028.55616898148</v>
+        <v>46028.52988425926</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D98" s="2">
-        <v>46028.72046296296</v>
+        <v>46028.72078703704</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="G98" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="G98" s="2">
+        <v>18.35</v>
+      </c>
       <c r="H98" s="2">
         <v>0</v>
       </c>
@@ -4038,7 +4246,7 @@
         <v>0</v>
       </c>
       <c r="J98" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="99" spans="1:10">
@@ -4046,21 +4254,23 @@
         <v>91</v>
       </c>
       <c r="B99" s="2">
-        <v>46028.30581018519</v>
+        <v>46028.31760416667</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D99" s="2">
-        <v>46028.53189814815</v>
+        <v>46028.50840277778</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="G99" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="G99" s="2">
+        <v>18.35</v>
+      </c>
       <c r="H99" s="2">
         <v>0</v>
       </c>
@@ -4068,7 +4278,7 @@
         <v>0</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="100" spans="1:10">
@@ -4076,21 +4286,23 @@
         <v>92</v>
       </c>
       <c r="B100" s="2">
-        <v>46028.52590277778</v>
+        <v>46028.60388888889</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D100" s="2">
-        <v>46028.72148148148</v>
+        <v>46028.72092592593</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="G100" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="G100" s="2">
+        <v>18.35</v>
+      </c>
       <c r="H100" s="2">
         <v>0</v>
       </c>
@@ -4098,29 +4310,31 @@
         <v>0</v>
       </c>
       <c r="J100" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="101" spans="1:10">
       <c r="A101" s="2" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B101" s="2">
-        <v>46028.32298611111</v>
+        <v>46028.32222222222</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D101" s="2">
-        <v>46028.60652777777</v>
+        <v>46028.54364583334</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="G101" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="G101" s="2">
+        <v>18.35</v>
+      </c>
       <c r="H101" s="2">
         <v>0</v>
       </c>
@@ -4128,29 +4342,31 @@
         <v>0</v>
       </c>
       <c r="J101" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="102" spans="1:10">
       <c r="A102" s="2" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="B102" s="2">
-        <v>46028.32238425926</v>
+        <v>46028.61898148148</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D102" s="2">
-        <v>46028.54351851852</v>
+        <v>46028.72040509259</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="G102" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="G102" s="2">
+        <v>19.6</v>
+      </c>
       <c r="H102" s="2">
         <v>0</v>
       </c>
@@ -4158,29 +4374,31 @@
         <v>0</v>
       </c>
       <c r="J102" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="103" spans="1:10">
       <c r="A103" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="B103" s="2">
-        <v>46028.60377314815</v>
+        <v>46028.32298611111</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D103" s="2">
-        <v>46028.70818287037</v>
+        <v>46028.60652777777</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="G103" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="G103" s="2">
+        <v>19.6</v>
+      </c>
       <c r="H103" s="2">
         <v>0</v>
       </c>
@@ -4188,29 +4406,31 @@
         <v>0</v>
       </c>
       <c r="J103" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="104" spans="1:10">
       <c r="A104" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B104" s="2">
-        <v>46028.30513888889</v>
+        <v>46028.30614583333</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D104" s="2">
-        <v>46028.58003472222</v>
+        <v>46028.54078703704</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="G104" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="G104" s="2">
+        <v>18.6</v>
+      </c>
       <c r="H104" s="2">
         <v>0</v>
       </c>
@@ -4218,29 +4438,31 @@
         <v>0</v>
       </c>
       <c r="J104" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="105" spans="1:10">
       <c r="A105" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B105" s="2">
-        <v>46028.33111111111</v>
+        <v>46028.55462962963</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D105" s="2">
-        <v>46028.5156712963</v>
+        <v>46028.72041666666</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="G105" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="G105" s="2">
+        <v>18.6</v>
+      </c>
       <c r="H105" s="2">
         <v>0</v>
       </c>
@@ -4248,29 +4470,31 @@
         <v>0</v>
       </c>
       <c r="J105" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="106" spans="1:10">
       <c r="A106" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B106" s="2">
-        <v>46028.61898148148</v>
+        <v>46028.32509259259</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D106" s="2">
-        <v>46028.72040509259</v>
+        <v>46028.58266203704</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="G106" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="G106" s="2">
+        <v>18.35</v>
+      </c>
       <c r="H106" s="2">
         <v>0</v>
       </c>
@@ -4278,29 +4502,31 @@
         <v>0</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="107" spans="1:10">
       <c r="A107" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B107" s="2">
-        <v>46028.32222222222</v>
+        <v>46028.60049768518</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D107" s="2">
-        <v>46028.54364583334</v>
+        <v>46028.72306712963</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="G107" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="G107" s="2">
+        <v>18.35</v>
+      </c>
       <c r="H107" s="2">
         <v>0</v>
       </c>
@@ -4308,7 +4534,7 @@
         <v>0</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="108" spans="1:10">
@@ -4316,21 +4542,23 @@
         <v>89</v>
       </c>
       <c r="B108" s="2">
-        <v>46028.59976851852</v>
+        <v>46028.33131944444</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D108" s="2">
-        <v>46028.72050925926</v>
+        <v>46028.53142361111</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="G108" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="G108" s="2">
+        <v>18.6</v>
+      </c>
       <c r="H108" s="2">
         <v>0</v>
       </c>
@@ -4338,29 +4566,31 @@
         <v>0</v>
       </c>
       <c r="J108" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="109" spans="1:10">
       <c r="A109" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B109" s="2">
-        <v>46028.60388888889</v>
+        <v>46028.56038194444</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D109" s="2">
-        <v>46028.72092592593</v>
+        <v>46028.72055555556</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="G109" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="G109" s="2">
+        <v>18.35</v>
+      </c>
       <c r="H109" s="2">
         <v>0</v>
       </c>
@@ -4368,29 +4598,31 @@
         <v>0</v>
       </c>
       <c r="J109" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="110" spans="1:10">
       <c r="A110" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B110" s="2">
-        <v>46028.33131944444</v>
+        <v>46028.29305555556</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D110" s="2">
-        <v>46028.53142361111</v>
+        <v>46028.49708333334</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="G110" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="G110" s="2">
+        <v>18.35</v>
+      </c>
       <c r="H110" s="2">
         <v>0</v>
       </c>
@@ -4398,29 +4630,31 @@
         <v>0</v>
       </c>
       <c r="J110" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="111" spans="1:10">
       <c r="A111" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B111" s="2">
-        <v>46028.54517361111</v>
+        <v>46028.32238425926</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D111" s="2">
-        <v>46028.72144675926</v>
+        <v>46028.54351851852</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="G111" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="G111" s="2">
+        <v>18.35</v>
+      </c>
       <c r="H111" s="2">
         <v>0</v>
       </c>
@@ -4428,29 +4662,31 @@
         <v>0</v>
       </c>
       <c r="J111" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="112" spans="1:10">
       <c r="A112" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B112" s="2">
-        <v>46028.30614583333</v>
+        <v>46028.31454861111</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D112" s="2">
-        <v>46028.54078703704</v>
+        <v>46028.53908564815</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="G112" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="G112" s="2">
+        <v>18.7</v>
+      </c>
       <c r="H112" s="2">
         <v>0</v>
       </c>
@@ -4458,7 +4694,7 @@
         <v>0</v>
       </c>
       <c r="J112" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="113" spans="1:10">
@@ -4466,21 +4702,23 @@
         <v>98</v>
       </c>
       <c r="B113" s="2">
-        <v>46028.55462962963</v>
+        <v>46028.60377314815</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D113" s="2">
-        <v>46028.72041666666</v>
+        <v>46028.70818287037</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="G113" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="G113" s="2">
+        <v>23</v>
+      </c>
       <c r="H113" s="2">
         <v>0</v>
       </c>
@@ -4488,29 +4726,31 @@
         <v>0</v>
       </c>
       <c r="J113" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="114" spans="1:10">
       <c r="A114" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B114" s="2">
-        <v>46028.53569444444</v>
+        <v>46028.30513888889</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D114" s="2">
-        <v>46028.72096064815</v>
+        <v>46028.58003472222</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="G114" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="G114" s="2">
+        <v>23</v>
+      </c>
       <c r="H114" s="2">
         <v>0</v>
       </c>
@@ -4518,29 +4758,31 @@
         <v>0</v>
       </c>
       <c r="J114" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="115" spans="1:10">
       <c r="A115" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B115" s="2">
-        <v>46028.60049768518</v>
+        <v>46028.52590277778</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D115" s="2">
-        <v>46028.72306712963</v>
+        <v>46028.72148148148</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="G115" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="G115" s="2">
+        <v>18.35</v>
+      </c>
       <c r="H115" s="2">
         <v>0</v>
       </c>
@@ -4548,29 +4790,31 @@
         <v>0</v>
       </c>
       <c r="J115" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="116" spans="1:10">
       <c r="A116" s="2" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="B116" s="2">
-        <v>46028.29305555556</v>
+        <v>46028.33111111111</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D116" s="2">
-        <v>46028.49708333334</v>
+        <v>46028.5156712963</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="G116" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="G116" s="2">
+        <v>18.35</v>
+      </c>
       <c r="H116" s="2">
         <v>0</v>
       </c>
@@ -4578,29 +4822,31 @@
         <v>0</v>
       </c>
       <c r="J116" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="117" spans="1:10">
       <c r="A117" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B117" s="2">
-        <v>46028.32494212963</v>
+        <v>46028.59063657407</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D117" s="2">
-        <v>46028.58037037037</v>
+        <v>46028.72025462963</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="G117" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="G117" s="2">
+        <v>18.6</v>
+      </c>
       <c r="H117" s="2">
         <v>0</v>
       </c>
@@ -4608,29 +4854,31 @@
         <v>0</v>
       </c>
       <c r="J117" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="118" spans="1:10">
       <c r="A118" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B118" s="2">
-        <v>46028.3316550926</v>
+        <v>46028.53569444444</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D118" s="2">
-        <v>46028.72032407407</v>
+        <v>46028.72096064815</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="G118" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="G118" s="2">
+        <v>18.35</v>
+      </c>
       <c r="H118" s="2">
         <v>0</v>
       </c>
@@ -4638,7 +4886,7 @@
         <v>0</v>
       </c>
       <c r="J118" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="119" spans="1:10">
@@ -4646,21 +4894,23 @@
         <v>101</v>
       </c>
       <c r="B119" s="2">
-        <v>46028.31760416667</v>
+        <v>46028.56594907407</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D119" s="2">
-        <v>46028.50840277778</v>
+        <v>46028.72104166666</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="G119" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="G119" s="2">
+        <v>18.7</v>
+      </c>
       <c r="H119" s="2">
         <v>0</v>
       </c>
@@ -4668,7 +4918,7 @@
         <v>0</v>
       </c>
       <c r="J119" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="120" spans="1:10">
@@ -4676,21 +4926,23 @@
         <v>101</v>
       </c>
       <c r="B120" s="2">
-        <v>46028.52988425926</v>
+        <v>46028.32545138889</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D120" s="2">
-        <v>46028.72078703704</v>
+        <v>46028.55892361111</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="G120" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="G120" s="2">
+        <v>18.7</v>
+      </c>
       <c r="H120" s="2">
         <v>0</v>
       </c>
@@ -4698,7 +4950,7 @@
         <v>0</v>
       </c>
       <c r="J120" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="121" spans="1:10">
@@ -4706,21 +4958,23 @@
         <v>102</v>
       </c>
       <c r="B121" s="2">
-        <v>46028.32545138889</v>
+        <v>46028.55616898148</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D121" s="2">
-        <v>46028.55892361111</v>
+        <v>46028.72046296296</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="G121" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="G121" s="2">
+        <v>18.35</v>
+      </c>
       <c r="H121" s="2">
         <v>0</v>
       </c>
@@ -4728,29 +4982,31 @@
         <v>0</v>
       </c>
       <c r="J121" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="122" spans="1:10">
       <c r="A122" s="2" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="B122" s="2">
-        <v>46028.56038194444</v>
+        <v>46028.30581018519</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D122" s="2">
-        <v>46028.72055555556</v>
+        <v>46028.53189814815</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="G122" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="G122" s="2">
+        <v>18.35</v>
+      </c>
       <c r="H122" s="2">
         <v>0</v>
       </c>
@@ -4758,29 +5014,31 @@
         <v>0</v>
       </c>
       <c r="J122" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="123" spans="1:10">
       <c r="A123" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B123" s="2">
-        <v>46028.56594907407</v>
+        <v>46028.3316550926</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D123" s="2">
-        <v>46028.72104166666</v>
+        <v>46028.72032407407</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="G123" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="G123" s="2">
+        <v>19.25</v>
+      </c>
       <c r="H123" s="2">
         <v>0</v>
       </c>
@@ -4788,29 +5046,31 @@
         <v>0</v>
       </c>
       <c r="J123" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="124" spans="1:10">
       <c r="A124" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B124" s="2">
-        <v>46028.59063657407</v>
+        <v>46028.32494212963</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D124" s="2">
-        <v>46028.72025462963</v>
+        <v>46028.58037037037</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="G124" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="G124" s="2">
+        <v>18.6</v>
+      </c>
       <c r="H124" s="2">
         <v>0</v>
       </c>
@@ -4818,29 +5078,31 @@
         <v>0</v>
       </c>
       <c r="J124" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="125" spans="1:10">
       <c r="A125" s="2" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="B125" s="2">
-        <v>46028.31454861111</v>
+        <v>46028.59976851852</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D125" s="2">
-        <v>46028.53908564815</v>
+        <v>46028.72050925926</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="G125" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="G125" s="2">
+        <v>19.75</v>
+      </c>
       <c r="H125" s="2">
         <v>0</v>
       </c>
@@ -4848,7 +5110,7 @@
         <v>0</v>
       </c>
       <c r="J125" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="126" spans="1:10">
@@ -4859,18 +5121,20 @@
         <v>46028.34119212963</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D126" s="2">
         <v>46028.68545138889</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="G126" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="G126" s="2">
+        <v>19.75</v>
+      </c>
       <c r="H126" s="2">
         <v>0</v>
       </c>
@@ -4878,7 +5142,7 @@
         <v>0</v>
       </c>
       <c r="J126" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="127" spans="1:10">
@@ -4886,21 +5150,23 @@
         <v>105</v>
       </c>
       <c r="B127" s="2">
-        <v>46028.34982638889</v>
+        <v>46028.60416666666</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D127" s="2">
-        <v>46028.58994212963</v>
+        <v>46028.70761574074</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="G127" s="2"/>
+        <v>203</v>
+      </c>
+      <c r="G127" s="2">
+        <v>18.35</v>
+      </c>
       <c r="H127" s="2">
         <v>0</v>
       </c>
@@ -4908,29 +5174,31 @@
         <v>0</v>
       </c>
       <c r="J127" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="128" spans="1:10">
       <c r="A128" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B128" s="2">
-        <v>46028.60416666666</v>
+        <v>46028.375</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D128" s="2">
-        <v>46028.70761574074</v>
+        <v>46028.589375</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="G128" s="2"/>
+        <v>203</v>
+      </c>
+      <c r="G128" s="2">
+        <v>18.35</v>
+      </c>
       <c r="H128" s="2">
         <v>0</v>
       </c>
@@ -4938,29 +5206,31 @@
         <v>0</v>
       </c>
       <c r="J128" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="129" spans="1:10">
       <c r="A129" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B129" s="2">
-        <v>46028.329375</v>
+        <v>46028.34982638889</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D129" s="2">
-        <v>46028.53986111111</v>
+        <v>46028.58994212963</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="G129" s="2"/>
+        <v>203</v>
+      </c>
+      <c r="G129" s="2">
+        <v>18.6</v>
+      </c>
       <c r="H129" s="2">
         <v>0</v>
       </c>
@@ -4968,29 +5238,31 @@
         <v>0</v>
       </c>
       <c r="J129" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="130" spans="1:10">
       <c r="A130" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B130" s="2">
-        <v>46028.375</v>
+        <v>46028.56010416667</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D130" s="2">
-        <v>46028.589375</v>
+        <v>46028.73116898148</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="G130" s="2"/>
+        <v>203</v>
+      </c>
+      <c r="G130" s="2">
+        <v>23</v>
+      </c>
       <c r="H130" s="2">
         <v>0</v>
       </c>
@@ -4998,7 +5270,7 @@
         <v>0</v>
       </c>
       <c r="J130" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="131" spans="1:10">
@@ -5006,21 +5278,23 @@
         <v>107</v>
       </c>
       <c r="B131" s="2">
-        <v>46028.56010416667</v>
+        <v>46028.329375</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D131" s="2">
-        <v>46028.73116898148</v>
+        <v>46028.53986111111</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="G131" s="2"/>
+        <v>203</v>
+      </c>
+      <c r="G131" s="2">
+        <v>23</v>
+      </c>
       <c r="H131" s="2">
         <v>0</v>
       </c>
@@ -5028,7 +5302,7 @@
         <v>0</v>
       </c>
       <c r="J131" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="132" spans="1:10">
@@ -5039,18 +5313,20 @@
         <v>46028.38664351852</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D132" s="2">
         <v>46028.71539351852</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="G132" s="2"/>
+        <v>204</v>
+      </c>
+      <c r="G132" s="2">
+        <v>18.6</v>
+      </c>
       <c r="H132" s="2">
         <v>0</v>
       </c>
@@ -5058,7 +5334,7 @@
         <v>0</v>
       </c>
       <c r="J132" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="133" spans="1:10">
@@ -5069,18 +5345,20 @@
         <v>46028.3221412037</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D133" s="2">
         <v>46028.69193287037</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="G133" s="2"/>
+        <v>205</v>
+      </c>
+      <c r="G133" s="2">
+        <v>25.7</v>
+      </c>
       <c r="H133" s="2">
         <v>0</v>
       </c>
@@ -5088,7 +5366,7 @@
         <v>0</v>
       </c>
       <c r="J133" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="134" spans="1:10">
@@ -5096,29 +5374,31 @@
         <v>110</v>
       </c>
       <c r="B134" s="2">
-        <v>46028.32587962963</v>
+        <v>46028.5</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D134" s="2">
-        <v>46028.60489583333</v>
+        <v>46028.5</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="G134" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="G134" s="2">
+        <v>20.7</v>
+      </c>
       <c r="H134" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I134" s="2">
         <v>0</v>
       </c>
       <c r="J134" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="135" spans="1:10">
@@ -5126,21 +5406,23 @@
         <v>111</v>
       </c>
       <c r="B135" s="2">
-        <v>46028.33752314815</v>
+        <v>46028.44420138889</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D135" s="2">
-        <v>46028.71677083334</v>
+        <v>46028.6834375</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="G135" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="G135" s="2">
+        <v>18.35</v>
+      </c>
       <c r="H135" s="2">
         <v>0</v>
       </c>
@@ -5148,7 +5430,7 @@
         <v>0</v>
       </c>
       <c r="J135" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="136" spans="1:10">
@@ -5156,21 +5438,23 @@
         <v>112</v>
       </c>
       <c r="B136" s="2">
-        <v>46028.45773148148</v>
+        <v>46028.33752314815</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D136" s="2">
-        <v>46028.68657407408</v>
+        <v>46028.71677083334</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="G136" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="G136" s="2">
+        <v>22.4</v>
+      </c>
       <c r="H136" s="2">
         <v>0</v>
       </c>
@@ -5178,7 +5462,7 @@
         <v>0</v>
       </c>
       <c r="J136" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="137" spans="1:10">
@@ -5186,31 +5470,31 @@
         <v>113</v>
       </c>
       <c r="B137" s="2">
-        <v>46028</v>
+        <v>46028.45773148148</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D137" s="2">
-        <v>46028</v>
+        <v>46028.68657407408</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G137" s="2">
-        <v>15.9</v>
+        <v>18.35</v>
       </c>
       <c r="H137" s="2">
         <v>0</v>
       </c>
       <c r="I137" s="2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J137" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="138" spans="1:10">
@@ -5218,21 +5502,23 @@
         <v>114</v>
       </c>
       <c r="B138" s="2">
-        <v>46028.44420138889</v>
+        <v>46028.37125</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D138" s="2">
-        <v>46028.6834375</v>
+        <v>46028.71365740741</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="G138" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="G138" s="2">
+        <v>15.9</v>
+      </c>
       <c r="H138" s="2">
         <v>0</v>
       </c>
@@ -5240,89 +5526,95 @@
         <v>0</v>
       </c>
       <c r="J138" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="139" spans="1:10">
       <c r="A139" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B139" s="2">
-        <v>46028.5</v>
+        <v>46028</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D139" s="2">
-        <v>46028.5</v>
+        <v>46028</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="G139" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="G139" s="2">
+        <v>15.9</v>
+      </c>
       <c r="H139" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I139" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J139" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="140" spans="1:10">
       <c r="A140" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B140" s="2">
-        <v>46028.33333333334</v>
+        <v>46028.32587962963</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D140" s="2">
-        <v>46028.33333333334</v>
+        <v>46028.60489583333</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="G140" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="G140" s="2">
+        <v>20.2</v>
+      </c>
       <c r="H140" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I140" s="2">
         <v>0</v>
       </c>
       <c r="J140" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="141" spans="1:10">
       <c r="A141" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B141" s="2">
         <v>46028.34849537037</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D141" s="2">
         <v>46028.67638888889</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="G141" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="G141" s="2">
+        <v>18.6</v>
+      </c>
       <c r="H141" s="2">
         <v>0</v>
       </c>
@@ -5330,29 +5622,31 @@
         <v>0</v>
       </c>
       <c r="J141" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="142" spans="1:10">
       <c r="A142" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B142" s="2">
-        <v>46028.25557870371</v>
+        <v>46028.37474537037</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D142" s="2">
-        <v>46028.68261574074</v>
+        <v>46028.75060185185</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="G142" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="G142" s="2">
+        <v>18.35</v>
+      </c>
       <c r="H142" s="2">
         <v>0</v>
       </c>
@@ -5360,39 +5654,39 @@
         <v>0</v>
       </c>
       <c r="J142" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="143" spans="1:10">
       <c r="A143" s="2" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="B143" s="2">
-        <v>46028.37125</v>
+        <v>46028.33333333334</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D143" s="2">
-        <v>46028.71365740741</v>
+        <v>46028.33333333334</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G143" s="2">
-        <v>15.9</v>
+        <v>18.35</v>
       </c>
       <c r="H143" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I143" s="2">
         <v>0</v>
       </c>
       <c r="J143" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="144" spans="1:10">
@@ -5400,21 +5694,23 @@
         <v>119</v>
       </c>
       <c r="B144" s="2">
-        <v>46028.37474537037</v>
+        <v>46028.25557870371</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D144" s="2">
-        <v>46028.75060185185</v>
+        <v>46028.68261574074</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="G144" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="G144" s="2">
+        <v>22.4</v>
+      </c>
       <c r="H144" s="2">
         <v>0</v>
       </c>
@@ -5422,7 +5718,7 @@
         <v>0</v>
       </c>
       <c r="J144" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="145" spans="1:10">
@@ -5430,21 +5726,23 @@
         <v>120</v>
       </c>
       <c r="B145" s="2">
-        <v>46028.26298611111</v>
+        <v>46028.26241898148</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D145" s="2">
-        <v>46028.6909837963</v>
+        <v>46028.6278587963</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="G145" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="G145" s="2">
+        <v>18.35</v>
+      </c>
       <c r="H145" s="2">
         <v>0</v>
       </c>
@@ -5452,7 +5750,7 @@
         <v>0</v>
       </c>
       <c r="J145" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="146" spans="1:10">
@@ -5460,29 +5758,31 @@
         <v>121</v>
       </c>
       <c r="B146" s="2">
-        <v>46028.37716435185</v>
+        <v>46028.33333333334</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D146" s="2">
-        <v>46028.67607638889</v>
+        <v>46028.33333333334</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="G146" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="G146" s="2">
+        <v>18.7</v>
+      </c>
       <c r="H146" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I146" s="2">
         <v>0</v>
       </c>
       <c r="J146" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="147" spans="1:10">
@@ -5490,29 +5790,31 @@
         <v>122</v>
       </c>
       <c r="B147" s="2">
-        <v>46028.33333333334</v>
+        <v>46028.37716435185</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D147" s="2">
-        <v>46028.33333333334</v>
+        <v>46028.67607638889</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="G147" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="G147" s="2">
+        <v>18.35</v>
+      </c>
       <c r="H147" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I147" s="2">
         <v>0</v>
       </c>
       <c r="J147" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="148" spans="1:10">
@@ -5520,29 +5822,31 @@
         <v>123</v>
       </c>
       <c r="B148" s="2">
-        <v>46028.33333333334</v>
+        <v>46028.46137731482</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D148" s="2">
-        <v>46028.33333333334</v>
+        <v>46028.70284722222</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="G148" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="G148" s="2">
+        <v>18.7</v>
+      </c>
       <c r="H148" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I148" s="2">
         <v>0</v>
       </c>
       <c r="J148" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="149" spans="1:10">
@@ -5550,21 +5854,23 @@
         <v>124</v>
       </c>
       <c r="B149" s="2">
-        <v>46028.45232638889</v>
+        <v>46028.31408564815</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D149" s="2">
-        <v>46028.67634259259</v>
+        <v>46028.62876157407</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="G149" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="G149" s="2">
+        <v>18.7</v>
+      </c>
       <c r="H149" s="2">
         <v>0</v>
       </c>
@@ -5572,7 +5878,7 @@
         <v>0</v>
       </c>
       <c r="J149" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="150" spans="1:10">
@@ -5580,29 +5886,31 @@
         <v>125</v>
       </c>
       <c r="B150" s="2">
-        <v>46028.33333333334</v>
+        <v>46028.45259259259</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D150" s="2">
-        <v>46028.33333333334</v>
+        <v>46028.70092592593</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="G150" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="G150" s="2">
+        <v>18.35</v>
+      </c>
       <c r="H150" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I150" s="2">
         <v>0</v>
       </c>
       <c r="J150" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="151" spans="1:10">
@@ -5610,21 +5918,23 @@
         <v>126</v>
       </c>
       <c r="B151" s="2">
-        <v>46028.31325231482</v>
+        <v>46028.40666666667</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D151" s="2">
-        <v>46028.63017361111</v>
+        <v>46028.74251157408</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="G151" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="G151" s="2">
+        <v>18.35</v>
+      </c>
       <c r="H151" s="2">
         <v>0</v>
       </c>
@@ -5632,29 +5942,31 @@
         <v>0</v>
       </c>
       <c r="J151" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="152" spans="1:10">
       <c r="A152" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B152" s="2">
-        <v>46028.41784722222</v>
+        <v>46028.33333333334</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D152" s="2">
-        <v>46028.6769212963</v>
+        <v>46028.37474537037</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="G152" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="G152" s="2">
+        <v>18.35</v>
+      </c>
       <c r="H152" s="2">
         <v>0</v>
       </c>
@@ -5662,59 +5974,63 @@
         <v>0</v>
       </c>
       <c r="J152" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="153" spans="1:10">
       <c r="A153" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B153" s="2">
         <v>46028.33333333334</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D153" s="2">
-        <v>46028.33333333334</v>
+        <v>46028.37474537037</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="G153" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="G153" s="2">
+        <v>18.35</v>
+      </c>
       <c r="H153" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I153" s="2">
         <v>0</v>
       </c>
       <c r="J153" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="154" spans="1:10">
       <c r="A154" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B154" s="2">
-        <v>46028.41054398148</v>
+        <v>46028.26295138889</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D154" s="2">
-        <v>46028.41194444444</v>
+        <v>46028.69109953703</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="G154" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="G154" s="2">
+        <v>19.65</v>
+      </c>
       <c r="H154" s="2">
         <v>0</v>
       </c>
@@ -5722,29 +6038,31 @@
         <v>0</v>
       </c>
       <c r="J154" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="155" spans="1:10">
       <c r="A155" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B155" s="2">
         <v>46028.50337962963</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D155" s="2">
         <v>46028.53291666666</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="G155" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="G155" s="2">
+        <v>23.35</v>
+      </c>
       <c r="H155" s="2">
         <v>0</v>
       </c>
@@ -5752,29 +6070,31 @@
         <v>0</v>
       </c>
       <c r="J155" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="156" spans="1:10">
       <c r="A156" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B156" s="2">
-        <v>46028.33333333334</v>
+        <v>46028.30770833333</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D156" s="2">
-        <v>46028.37474537037</v>
+        <v>46028.624375</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="G156" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="G156" s="2">
+        <v>18.35</v>
+      </c>
       <c r="H156" s="2">
         <v>0</v>
       </c>
@@ -5782,7 +6102,7 @@
         <v>0</v>
       </c>
       <c r="J156" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="157" spans="1:10">
@@ -5793,78 +6113,84 @@
         <v>46028.33333333334</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D157" s="2">
-        <v>46028.37474537037</v>
+        <v>46028.33333333334</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="G157" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="G157" s="2">
+        <v>18.35</v>
+      </c>
       <c r="H157" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I157" s="2">
         <v>0</v>
       </c>
       <c r="J157" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="158" spans="1:10">
       <c r="A158" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B158" s="2">
-        <v>46028.40666666667</v>
+        <v>46028.33333333334</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D158" s="2">
-        <v>46028.74251157408</v>
+        <v>46028.33333333334</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="G158" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="G158" s="2">
+        <v>18.35</v>
+      </c>
       <c r="H158" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I158" s="2">
         <v>0</v>
       </c>
       <c r="J158" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="159" spans="1:10">
       <c r="A159" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B159" s="2">
-        <v>46028.31408564815</v>
+        <v>46028.31325231482</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D159" s="2">
-        <v>46028.62876157407</v>
+        <v>46028.63017361111</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="G159" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="G159" s="2">
+        <v>18.35</v>
+      </c>
       <c r="H159" s="2">
         <v>0</v>
       </c>
@@ -5872,29 +6198,31 @@
         <v>0</v>
       </c>
       <c r="J159" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="160" spans="1:10">
       <c r="A160" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B160" s="2">
-        <v>46028.46137731482</v>
+        <v>46028.45232638889</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D160" s="2">
-        <v>46028.70284722222</v>
+        <v>46028.67634259259</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="G160" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="G160" s="2">
+        <v>18.35</v>
+      </c>
       <c r="H160" s="2">
         <v>0</v>
       </c>
@@ -5902,29 +6230,31 @@
         <v>0</v>
       </c>
       <c r="J160" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="161" spans="1:10">
       <c r="A161" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B161" s="2">
-        <v>46028.28449074074</v>
+        <v>46028.41784722222</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D161" s="2">
-        <v>46028.65356481481</v>
+        <v>46028.6769212963</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="G161" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="G161" s="2">
+        <v>18.35</v>
+      </c>
       <c r="H161" s="2">
         <v>0</v>
       </c>
@@ -5932,61 +6262,63 @@
         <v>0</v>
       </c>
       <c r="J161" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="162" spans="1:10">
       <c r="A162" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B162" s="2">
-        <v>46028.26295138889</v>
+        <v>46028.33333333334</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D162" s="2">
-        <v>46028.69109953703</v>
+        <v>46028.33333333334</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G162" s="2">
-        <v>19.65</v>
+        <v>18.35</v>
       </c>
       <c r="H162" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I162" s="2">
         <v>0</v>
       </c>
       <c r="J162" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="163" spans="1:10">
       <c r="A163" s="2" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="B163" s="2">
-        <v>46028.45259259259</v>
+        <v>46028.41054398148</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D163" s="2">
-        <v>46028.70092592593</v>
+        <v>46028.41194444444</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="G163" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="G163" s="2">
+        <v>23.35</v>
+      </c>
       <c r="H163" s="2">
         <v>0</v>
       </c>
@@ -5994,7 +6326,7 @@
         <v>0</v>
       </c>
       <c r="J163" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="164" spans="1:10">
@@ -6005,18 +6337,20 @@
         <v>46028.37892361111</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D164" s="2">
         <v>46028.67502314815</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="G164" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="G164" s="2">
+        <v>18.35</v>
+      </c>
       <c r="H164" s="2">
         <v>0</v>
       </c>
@@ -6024,7 +6358,7 @@
         <v>0</v>
       </c>
       <c r="J164" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="165" spans="1:10">
@@ -6032,21 +6366,23 @@
         <v>137</v>
       </c>
       <c r="B165" s="2">
-        <v>46028.30773148148</v>
+        <v>46028.28449074074</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D165" s="2">
-        <v>46028.6234837963</v>
+        <v>46028.65356481481</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="G165" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="G165" s="2">
+        <v>18.35</v>
+      </c>
       <c r="H165" s="2">
         <v>0</v>
       </c>
@@ -6054,7 +6390,7 @@
         <v>0</v>
       </c>
       <c r="J165" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="166" spans="1:10">
@@ -6065,18 +6401,20 @@
         <v>46028.31259259259</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D166" s="2">
         <v>46028.6283912037</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="G166" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="G166" s="2">
+        <v>18.35</v>
+      </c>
       <c r="H166" s="2">
         <v>0</v>
       </c>
@@ -6084,7 +6422,7 @@
         <v>0</v>
       </c>
       <c r="J166" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="167" spans="1:10">
@@ -6092,21 +6430,23 @@
         <v>139</v>
       </c>
       <c r="B167" s="2">
-        <v>46028.46034722222</v>
+        <v>46028.30773148148</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D167" s="2">
-        <v>46028.70288194445</v>
+        <v>46028.6234837963</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="G167" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="G167" s="2">
+        <v>18.35</v>
+      </c>
       <c r="H167" s="2">
         <v>0</v>
       </c>
@@ -6114,7 +6454,7 @@
         <v>0</v>
       </c>
       <c r="J167" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="168" spans="1:10">
@@ -6122,22 +6462,22 @@
         <v>140</v>
       </c>
       <c r="B168" s="2">
-        <v>46028.30770833333</v>
+        <v>46028.26298611111</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D168" s="2">
-        <v>46028.624375</v>
+        <v>46028.6909837963</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G168" s="2">
-        <v>18.35</v>
+        <v>23.35</v>
       </c>
       <c r="H168" s="2">
         <v>0</v>
@@ -6146,7 +6486,7 @@
         <v>0</v>
       </c>
       <c r="J168" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="169" spans="1:10">
@@ -6154,21 +6494,23 @@
         <v>141</v>
       </c>
       <c r="B169" s="2">
-        <v>46028.26241898148</v>
+        <v>46028.46034722222</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D169" s="2">
-        <v>46028.6278587963</v>
+        <v>46028.70288194445</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="G169" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="G169" s="2">
+        <v>18.35</v>
+      </c>
       <c r="H169" s="2">
         <v>0</v>
       </c>
@@ -6176,7 +6518,7 @@
         <v>0</v>
       </c>
       <c r="J169" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="170" spans="1:10">
@@ -6184,21 +6526,23 @@
         <v>142</v>
       </c>
       <c r="B170" s="2">
-        <v>46028.57543981481</v>
+        <v>46028.56887731481</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D170" s="2">
-        <v>46028.89612268518</v>
+        <v>46028.89061342592</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="G170" s="2"/>
+        <v>208</v>
+      </c>
+      <c r="G170" s="2">
+        <v>19.25</v>
+      </c>
       <c r="H170" s="2">
         <v>0</v>
       </c>
@@ -6206,7 +6550,7 @@
         <v>0</v>
       </c>
       <c r="J170" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="171" spans="1:10">
@@ -6214,21 +6558,23 @@
         <v>143</v>
       </c>
       <c r="B171" s="2">
-        <v>46028.56887731481</v>
+        <v>46028.57543981481</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D171" s="2">
-        <v>46028.89061342592</v>
+        <v>46028.89612268518</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="G171" s="2"/>
+        <v>208</v>
+      </c>
+      <c r="G171" s="2">
+        <v>18.35</v>
+      </c>
       <c r="H171" s="2">
         <v>0</v>
       </c>
@@ -6236,7 +6582,7 @@
         <v>0</v>
       </c>
       <c r="J171" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="172" spans="1:10">
@@ -6244,21 +6590,23 @@
         <v>144</v>
       </c>
       <c r="B172" s="2">
-        <v>46028.37171296297</v>
+        <v>46028.37355324074</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D172" s="2">
-        <v>46028.70578703703</v>
+        <v>46028.68474537037</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="G172" s="2"/>
+        <v>209</v>
+      </c>
+      <c r="G172" s="2">
+        <v>18.35</v>
+      </c>
       <c r="H172" s="2">
         <v>0</v>
       </c>
@@ -6266,7 +6614,7 @@
         <v>0</v>
       </c>
       <c r="J172" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="173" spans="1:10">
@@ -6274,21 +6622,23 @@
         <v>145</v>
       </c>
       <c r="B173" s="2">
-        <v>46028.37355324074</v>
+        <v>46028.37171296297</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D173" s="2">
-        <v>46028.68474537037</v>
+        <v>46028.70578703703</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="G173" s="2"/>
+        <v>209</v>
+      </c>
+      <c r="G173" s="2">
+        <v>25.7</v>
+      </c>
       <c r="H173" s="2">
         <v>0</v>
       </c>
@@ -6296,7 +6646,7 @@
         <v>0</v>
       </c>
       <c r="J173" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="174" spans="1:10">
@@ -6304,21 +6654,23 @@
         <v>146</v>
       </c>
       <c r="B174" s="2">
-        <v>46028.41197916667</v>
+        <v>46028.36895833333</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D174" s="2">
-        <v>46028.61369212963</v>
+        <v>46028.60674768518</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="G174" s="2"/>
+        <v>209</v>
+      </c>
+      <c r="G174" s="2">
+        <v>18.7</v>
+      </c>
       <c r="H174" s="2">
         <v>0</v>
       </c>
@@ -6326,7 +6678,7 @@
         <v>0</v>
       </c>
       <c r="J174" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="175" spans="1:10">
@@ -6334,21 +6686,23 @@
         <v>147</v>
       </c>
       <c r="B175" s="2">
-        <v>46028.36895833333</v>
+        <v>46028.38260416667</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D175" s="2">
-        <v>46028.60674768518</v>
+        <v>46028.70351851852</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="G175" s="2"/>
+        <v>209</v>
+      </c>
+      <c r="G175" s="2">
+        <v>23.35</v>
+      </c>
       <c r="H175" s="2">
         <v>0</v>
       </c>
@@ -6356,7 +6710,7 @@
         <v>0</v>
       </c>
       <c r="J175" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="176" spans="1:10">
@@ -6364,21 +6718,23 @@
         <v>148</v>
       </c>
       <c r="B176" s="2">
-        <v>46028.38260416667</v>
+        <v>46028.41197916667</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D176" s="2">
-        <v>46028.70351851852</v>
+        <v>46028.61369212963</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="G176" s="2"/>
+        <v>209</v>
+      </c>
+      <c r="G176" s="2">
+        <v>18.35</v>
+      </c>
       <c r="H176" s="2">
         <v>0</v>
       </c>
@@ -6386,7 +6742,7 @@
         <v>0</v>
       </c>
       <c r="J176" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="177" spans="1:10">
@@ -6394,22 +6750,22 @@
         <v>149</v>
       </c>
       <c r="B177" s="2">
-        <v>46028.90663194445</v>
+        <v>46028.27663194444</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D177" s="2">
-        <v>46029.12541666667</v>
+        <v>46028.55585648148</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G177" s="2">
-        <v>19.65</v>
+        <v>20.2</v>
       </c>
       <c r="H177" s="2">
         <v>0</v>
@@ -6418,7 +6774,7 @@
         <v>0</v>
       </c>
       <c r="J177" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="178" spans="1:10">
@@ -6426,21 +6782,23 @@
         <v>150</v>
       </c>
       <c r="B178" s="2">
-        <v>46028.61616898148</v>
+        <v>46028.90663194445</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D178" s="2">
-        <v>46028.9105324074</v>
+        <v>46029.12541666667</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="G178" s="2"/>
+        <v>210</v>
+      </c>
+      <c r="G178" s="2">
+        <v>19.65</v>
+      </c>
       <c r="H178" s="2">
         <v>0</v>
       </c>
@@ -6448,7 +6806,7 @@
         <v>0</v>
       </c>
       <c r="J178" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="179" spans="1:10">
@@ -6456,21 +6814,23 @@
         <v>151</v>
       </c>
       <c r="B179" s="2">
-        <v>46028.27663194444</v>
+        <v>46028.61616898148</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D179" s="2">
-        <v>46028.55585648148</v>
+        <v>46028.9105324074</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="G179" s="2"/>
+        <v>210</v>
+      </c>
+      <c r="G179" s="2">
+        <v>18.35</v>
+      </c>
       <c r="H179" s="2">
         <v>0</v>
       </c>
@@ -6478,7 +6838,7 @@
         <v>0</v>
       </c>
       <c r="J179" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="180" spans="1:10">
@@ -6489,18 +6849,20 @@
         <v>46028.69038194444</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D180" s="2">
         <v>46028.87313657408</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="G180" s="2"/>
+        <v>211</v>
+      </c>
+      <c r="G180" s="2">
+        <v>22.4</v>
+      </c>
       <c r="H180" s="2">
         <v>0</v>
       </c>
@@ -6508,7 +6870,7 @@
         <v>0</v>
       </c>
       <c r="J180" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="181" spans="1:10">
@@ -6516,21 +6878,23 @@
         <v>153</v>
       </c>
       <c r="B181" s="2">
-        <v>46028.38710648148</v>
+        <v>46028.37621527778</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D181" s="2">
-        <v>46028.62877314815</v>
+        <v>46028.61886574074</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="G181" s="2"/>
+        <v>211</v>
+      </c>
+      <c r="G181" s="2">
+        <v>20.2</v>
+      </c>
       <c r="H181" s="2">
         <v>0</v>
       </c>
@@ -6538,7 +6902,7 @@
         <v>0</v>
       </c>
       <c r="J181" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="182" spans="1:10">
@@ -6546,21 +6910,23 @@
         <v>154</v>
       </c>
       <c r="B182" s="2">
-        <v>46028.37621527778</v>
+        <v>46028.38710648148</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D182" s="2">
-        <v>46028.61886574074</v>
+        <v>46028.62877314815</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="G182" s="2"/>
+        <v>211</v>
+      </c>
+      <c r="G182" s="2">
+        <v>20.2</v>
+      </c>
       <c r="H182" s="2">
         <v>0</v>
       </c>
@@ -6568,7 +6934,7 @@
         <v>0</v>
       </c>
       <c r="J182" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="183" spans="1:10">
@@ -6579,18 +6945,20 @@
         <v>46028.46222222222</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D183" s="2">
         <v>46028.68123842592</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="G183" s="2"/>
+        <v>211</v>
+      </c>
+      <c r="G183" s="2">
+        <v>23</v>
+      </c>
       <c r="H183" s="2">
         <v>0</v>
       </c>
@@ -6598,7 +6966,7 @@
         <v>0</v>
       </c>
       <c r="J183" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="184" spans="1:10">
@@ -6606,19 +6974,19 @@
         <v>156</v>
       </c>
       <c r="B184" s="2">
-        <v>46028.30685185185</v>
+        <v>46028.31606481481</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D184" s="2">
-        <v>46028.76862268519</v>
+        <v>46028.51908564815</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G184" s="2">
         <v>19.65</v>
@@ -6630,7 +6998,7 @@
         <v>0</v>
       </c>
       <c r="J184" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="185" spans="1:10">
@@ -6638,29 +7006,31 @@
         <v>157</v>
       </c>
       <c r="B185" s="2">
-        <v>46028.34049768518</v>
+        <v>46028.5</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D185" s="2">
-        <v>46028.53296296296</v>
+        <v>46028.5</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="G185" s="2"/>
+        <v>212</v>
+      </c>
+      <c r="G185" s="2">
+        <v>19.6</v>
+      </c>
       <c r="H185" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I185" s="2">
         <v>0</v>
       </c>
       <c r="J185" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="186" spans="1:10">
@@ -6668,21 +7038,23 @@
         <v>158</v>
       </c>
       <c r="B186" s="2">
-        <v>46028.33634259259</v>
+        <v>46028.30685185185</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D186" s="2">
-        <v>46028.53591435185</v>
+        <v>46028.76862268519</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="G186" s="2"/>
+        <v>212</v>
+      </c>
+      <c r="G186" s="2">
+        <v>19.65</v>
+      </c>
       <c r="H186" s="2">
         <v>0</v>
       </c>
@@ -6690,7 +7062,7 @@
         <v>0</v>
       </c>
       <c r="J186" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="187" spans="1:10">
@@ -6698,29 +7070,31 @@
         <v>159</v>
       </c>
       <c r="B187" s="2">
-        <v>46028.33333333334</v>
+        <v>46028.34049768518</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D187" s="2">
-        <v>46028.33333333334</v>
+        <v>46028.53296296296</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="G187" s="2"/>
+        <v>212</v>
+      </c>
+      <c r="G187" s="2">
+        <v>19.25</v>
+      </c>
       <c r="H187" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I187" s="2">
         <v>0</v>
       </c>
       <c r="J187" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="188" spans="1:10">
@@ -6728,22 +7102,22 @@
         <v>160</v>
       </c>
       <c r="B188" s="2">
-        <v>46028.31606481481</v>
+        <v>46028.33423611111</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D188" s="2">
-        <v>46028.51908564815</v>
+        <v>46028.54413194444</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G188" s="2">
-        <v>19.65</v>
+        <v>19.6</v>
       </c>
       <c r="H188" s="2">
         <v>0</v>
@@ -6752,7 +7126,7 @@
         <v>0</v>
       </c>
       <c r="J188" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="189" spans="1:10">
@@ -6760,29 +7134,31 @@
         <v>161</v>
       </c>
       <c r="B189" s="2">
-        <v>46028.33423611111</v>
+        <v>46028.33333333334</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D189" s="2">
-        <v>46028.54413194444</v>
+        <v>46028.33333333334</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="G189" s="2"/>
+        <v>212</v>
+      </c>
+      <c r="G189" s="2">
+        <v>19.25</v>
+      </c>
       <c r="H189" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I189" s="2">
         <v>0</v>
       </c>
       <c r="J189" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="190" spans="1:10">
@@ -6790,29 +7166,31 @@
         <v>162</v>
       </c>
       <c r="B190" s="2">
-        <v>46028.5</v>
+        <v>46028.33634259259</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D190" s="2">
-        <v>46028.5</v>
+        <v>46028.53591435185</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="G190" s="2"/>
+        <v>212</v>
+      </c>
+      <c r="G190" s="2">
+        <v>19.25</v>
+      </c>
       <c r="H190" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I190" s="2">
         <v>0</v>
       </c>
       <c r="J190" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="191" spans="1:10">
@@ -6820,21 +7198,23 @@
         <v>163</v>
       </c>
       <c r="B191" s="2">
-        <v>46028.37875</v>
+        <v>46028.45947916667</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D191" s="2">
-        <v>46028.60488425926</v>
+        <v>46028.639375</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="G191" s="2"/>
+        <v>213</v>
+      </c>
+      <c r="G191" s="2">
+        <v>24.8</v>
+      </c>
       <c r="H191" s="2">
         <v>0</v>
       </c>
@@ -6842,29 +7222,31 @@
         <v>0</v>
       </c>
       <c r="J191" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="192" spans="1:10">
       <c r="A192" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B192" s="2">
-        <v>46028.71460648148</v>
+        <v>46028.65928240741</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D192" s="2">
-        <v>46028.87328703704</v>
+        <v>46028.77935185185</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="G192" s="2"/>
+        <v>213</v>
+      </c>
+      <c r="G192" s="2">
+        <v>24.8</v>
+      </c>
       <c r="H192" s="2">
         <v>0</v>
       </c>
@@ -6872,29 +7254,31 @@
         <v>0</v>
       </c>
       <c r="J192" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="193" spans="1:10">
       <c r="A193" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B193" s="2">
-        <v>46028.57635416667</v>
+        <v>46028.69549768518</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D193" s="2">
-        <v>46028.68651620371</v>
+        <v>46028.69550925926</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="G193" s="2"/>
+        <v>213</v>
+      </c>
+      <c r="G193" s="2">
+        <v>21.2</v>
+      </c>
       <c r="H193" s="2">
         <v>0</v>
       </c>
@@ -6902,29 +7286,31 @@
         <v>0</v>
       </c>
       <c r="J193" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="194" spans="1:10">
       <c r="A194" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B194" s="2">
-        <v>46028.45947916667</v>
+        <v>46028.33333333334</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D194" s="2">
-        <v>46028.639375</v>
+        <v>46028.52068287037</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="G194" s="2"/>
+        <v>213</v>
+      </c>
+      <c r="G194" s="2">
+        <v>21.2</v>
+      </c>
       <c r="H194" s="2">
         <v>0</v>
       </c>
@@ -6932,29 +7318,31 @@
         <v>0</v>
       </c>
       <c r="J194" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="195" spans="1:10">
       <c r="A195" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B195" s="2">
-        <v>46028.69649305556</v>
+        <v>46028.68194444444</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D195" s="2">
-        <v>46028.87337962963</v>
+        <v>46028.85853009259</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="G195" s="2"/>
+        <v>213</v>
+      </c>
+      <c r="G195" s="2">
+        <v>23</v>
+      </c>
       <c r="H195" s="2">
         <v>0</v>
       </c>
@@ -6962,29 +7350,31 @@
         <v>0</v>
       </c>
       <c r="J195" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="196" spans="1:10">
       <c r="A196" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B196" s="2">
-        <v>46028.68194444444</v>
+        <v>46028.69649305556</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D196" s="2">
-        <v>46028.85853009259</v>
+        <v>46028.87337962963</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="G196" s="2"/>
+        <v>213</v>
+      </c>
+      <c r="G196" s="2">
+        <v>20.7</v>
+      </c>
       <c r="H196" s="2">
         <v>0</v>
       </c>
@@ -6992,29 +7382,31 @@
         <v>0</v>
       </c>
       <c r="J196" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="197" spans="1:10">
       <c r="A197" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B197" s="2">
-        <v>46028.65928240741</v>
+        <v>46028.71460648148</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D197" s="2">
-        <v>46028.77935185185</v>
+        <v>46028.87328703704</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="G197" s="2"/>
+        <v>213</v>
+      </c>
+      <c r="G197" s="2">
+        <v>21.45</v>
+      </c>
       <c r="H197" s="2">
         <v>0</v>
       </c>
@@ -7022,29 +7414,31 @@
         <v>0</v>
       </c>
       <c r="J197" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="198" spans="1:10">
       <c r="A198" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B198" s="2">
-        <v>46028.69549768518</v>
+        <v>46028.57635416667</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D198" s="2">
-        <v>46028.69550925926</v>
+        <v>46028.68651620371</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="G198" s="2"/>
+        <v>213</v>
+      </c>
+      <c r="G198" s="2">
+        <v>20.7</v>
+      </c>
       <c r="H198" s="2">
         <v>0</v>
       </c>
@@ -7052,29 +7446,31 @@
         <v>0</v>
       </c>
       <c r="J198" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="199" spans="1:10">
       <c r="A199" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B199" s="2">
         <v>46028.70635416666</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D199" s="2">
         <v>46028.87307870371</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="G199" s="2"/>
+        <v>213</v>
+      </c>
+      <c r="G199" s="2">
+        <v>21.2</v>
+      </c>
       <c r="H199" s="2">
         <v>0</v>
       </c>
@@ -7082,29 +7478,31 @@
         <v>0</v>
       </c>
       <c r="J199" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="200" spans="1:10">
       <c r="A200" s="2" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="B200" s="2">
-        <v>46028.62547453704</v>
+        <v>46028.3313425926</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D200" s="2">
-        <v>46028.6912037037</v>
+        <v>46028.55741898148</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="G200" s="2"/>
+        <v>213</v>
+      </c>
+      <c r="G200" s="2">
+        <v>20.7</v>
+      </c>
       <c r="H200" s="2">
         <v>0</v>
       </c>
@@ -7112,29 +7510,31 @@
         <v>0</v>
       </c>
       <c r="J200" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="201" spans="1:10">
       <c r="A201" s="2" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B201" s="2">
-        <v>46028.3313425926</v>
+        <v>46028.62547453704</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D201" s="2">
-        <v>46028.55741898148</v>
+        <v>46028.6912037037</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="G201" s="2"/>
+        <v>213</v>
+      </c>
+      <c r="G201" s="2">
+        <v>20.7</v>
+      </c>
       <c r="H201" s="2">
         <v>0</v>
       </c>
@@ -7142,29 +7542,31 @@
         <v>0</v>
       </c>
       <c r="J201" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="202" spans="1:10">
       <c r="A202" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B202" s="2">
-        <v>46028.33333333334</v>
+        <v>46028.37875</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D202" s="2">
-        <v>46028.52068287037</v>
+        <v>46028.60488425926</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="G202" s="2"/>
+        <v>213</v>
+      </c>
+      <c r="G202" s="2">
+        <v>20.7</v>
+      </c>
       <c r="H202" s="2">
         <v>0</v>
       </c>
@@ -7172,7 +7574,7 @@
         <v>0</v>
       </c>
       <c r="J202" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="203" spans="1:10">
@@ -7180,21 +7582,23 @@
         <v>171</v>
       </c>
       <c r="B203" s="2">
-        <v>46028.58524305555</v>
+        <v>46028.38790509259</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D203" s="2">
-        <v>46028.76521990741</v>
+        <v>46028.56123842593</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="G203" s="2"/>
+        <v>214</v>
+      </c>
+      <c r="G203" s="2">
+        <v>26.8</v>
+      </c>
       <c r="H203" s="2">
         <v>0</v>
       </c>
@@ -7202,29 +7606,31 @@
         <v>0</v>
       </c>
       <c r="J203" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="204" spans="1:10">
       <c r="A204" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B204" s="2">
-        <v>46028.29490740741</v>
+        <v>46028.58524305555</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D204" s="2">
-        <v>46028.67212962963</v>
+        <v>46028.76521990741</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="G204" s="2"/>
+        <v>214</v>
+      </c>
+      <c r="G204" s="2">
+        <v>26.8</v>
+      </c>
       <c r="H204" s="2">
         <v>0</v>
       </c>
@@ -7232,29 +7638,31 @@
         <v>0</v>
       </c>
       <c r="J204" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="205" spans="1:10">
       <c r="A205" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B205" s="2">
-        <v>46028.38790509259</v>
+        <v>46028.32177083333</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D205" s="2">
-        <v>46028.56123842593</v>
+        <v>46028.68041666667</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="G205" s="2"/>
+        <v>214</v>
+      </c>
+      <c r="G205" s="2">
+        <v>26.5</v>
+      </c>
       <c r="H205" s="2">
         <v>0</v>
       </c>
@@ -7262,7 +7670,7 @@
         <v>0</v>
       </c>
       <c r="J205" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="206" spans="1:10">
@@ -7270,29 +7678,31 @@
         <v>173</v>
       </c>
       <c r="B206" s="2">
-        <v>46028.32177083333</v>
+        <v>46028.5</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D206" s="2">
-        <v>46028.68041666667</v>
+        <v>46028.5</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="G206" s="2"/>
+        <v>214</v>
+      </c>
+      <c r="G206" s="2">
+        <v>0</v>
+      </c>
       <c r="H206" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I206" s="2">
         <v>0</v>
       </c>
       <c r="J206" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="207" spans="1:10">
@@ -7300,21 +7710,23 @@
         <v>174</v>
       </c>
       <c r="B207" s="2">
-        <v>46028.30459490741</v>
+        <v>46028.29490740741</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D207" s="2">
-        <v>46028.71524305556</v>
+        <v>46028.67212962963</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="G207" s="2"/>
+        <v>214</v>
+      </c>
+      <c r="G207" s="2">
+        <v>26.45</v>
+      </c>
       <c r="H207" s="2">
         <v>0</v>
       </c>
@@ -7322,7 +7734,7 @@
         <v>0</v>
       </c>
       <c r="J207" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="208" spans="1:10">
@@ -7330,21 +7742,23 @@
         <v>175</v>
       </c>
       <c r="B208" s="2">
-        <v>46028.33693287037</v>
+        <v>46028.30459490741</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D208" s="2">
-        <v>46028.71986111111</v>
+        <v>46028.71524305556</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="G208" s="2"/>
+        <v>215</v>
+      </c>
+      <c r="G208" s="2">
+        <v>33.81</v>
+      </c>
       <c r="H208" s="2">
         <v>0</v>
       </c>
@@ -7352,7 +7766,7 @@
         <v>0</v>
       </c>
       <c r="J208" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="209" spans="1:10">
@@ -7360,21 +7774,23 @@
         <v>176</v>
       </c>
       <c r="B209" s="2">
-        <v>46028.33550925926</v>
+        <v>46028.33693287037</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D209" s="2">
-        <v>46028.70025462963</v>
+        <v>46028.71986111111</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="G209" s="2"/>
+        <v>215</v>
+      </c>
+      <c r="G209" s="2">
+        <v>30.78</v>
+      </c>
       <c r="H209" s="2">
         <v>0</v>
       </c>
@@ -7382,7 +7798,7 @@
         <v>0</v>
       </c>
       <c r="J209" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="210" spans="1:10">
@@ -7390,21 +7806,23 @@
         <v>177</v>
       </c>
       <c r="B210" s="2">
-        <v>46028.36075231482</v>
+        <v>46028.33550925926</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D210" s="2">
-        <v>46028.51035879629</v>
+        <v>46028.70025462963</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="G210" s="2"/>
+        <v>216</v>
+      </c>
+      <c r="G210" s="2">
+        <v>23</v>
+      </c>
       <c r="H210" s="2">
         <v>0</v>
       </c>
@@ -7412,7 +7830,7 @@
         <v>0</v>
       </c>
       <c r="J210" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="211" spans="1:10">
@@ -7420,21 +7838,23 @@
         <v>178</v>
       </c>
       <c r="B211" s="2">
-        <v>46028.33420138889</v>
+        <v>46028.375</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D211" s="2">
-        <v>46028.66133101852</v>
+        <v>46028.625</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="G211" s="2"/>
+        <v>216</v>
+      </c>
+      <c r="G211" s="2">
+        <v>23</v>
+      </c>
       <c r="H211" s="2">
         <v>0</v>
       </c>
@@ -7442,7 +7862,7 @@
         <v>0</v>
       </c>
       <c r="J211" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="212" spans="1:10">
@@ -7450,21 +7870,23 @@
         <v>179</v>
       </c>
       <c r="B212" s="2">
-        <v>46028.30923611111</v>
+        <v>46028.36075231482</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D212" s="2">
-        <v>46028.71655092593</v>
+        <v>46028.51035879629</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="G212" s="2"/>
+        <v>217</v>
+      </c>
+      <c r="G212" s="2">
+        <v>23</v>
+      </c>
       <c r="H212" s="2">
         <v>0</v>
       </c>
@@ -7472,29 +7894,31 @@
         <v>0</v>
       </c>
       <c r="J212" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="213" spans="1:10">
       <c r="A213" s="2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B213" s="2">
-        <v>46028.53652777777</v>
+        <v>46028.33420138889</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D213" s="2">
-        <v>46028.68799768519</v>
+        <v>46028.66133101852</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="G213" s="2"/>
+        <v>217</v>
+      </c>
+      <c r="G213" s="2">
+        <v>26.75</v>
+      </c>
       <c r="H213" s="2">
         <v>0</v>
       </c>
@@ -7502,29 +7926,31 @@
         <v>0</v>
       </c>
       <c r="J213" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="214" spans="1:10">
       <c r="A214" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B214" s="2">
-        <v>46028.33280092593</v>
+        <v>46028.30923611111</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D214" s="2">
-        <v>46028.66993055555</v>
+        <v>46028.71655092593</v>
       </c>
       <c r="E214" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="G214" s="2"/>
+        <v>217</v>
+      </c>
+      <c r="G214" s="2">
+        <v>21.4</v>
+      </c>
       <c r="H214" s="2">
         <v>0</v>
       </c>
@@ -7532,37 +7958,103 @@
         <v>0</v>
       </c>
       <c r="J214" s="2" t="s">
-        <v>185</v>
+        <v>248</v>
       </c>
     </row>
     <row r="215" spans="1:10">
       <c r="A215" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B215" s="2">
+        <v>46028.53652777777</v>
+      </c>
+      <c r="C215" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D215" s="2">
+        <v>46028.68799768519</v>
+      </c>
+      <c r="E215" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="F215" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="G215" s="2">
+        <v>23</v>
+      </c>
+      <c r="H215" s="2">
+        <v>0</v>
+      </c>
+      <c r="I215" s="2">
+        <v>0</v>
+      </c>
+      <c r="J215" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="216" spans="1:10">
+      <c r="A216" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B216" s="2">
         <v>46028.32597222222</v>
       </c>
-      <c r="C215" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="D215" s="2">
+      <c r="C216" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D216" s="2">
         <v>46028.65019675926</v>
       </c>
-      <c r="E215" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="F215" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="G215" s="2"/>
-      <c r="H215" s="2">
-        <v>0</v>
-      </c>
-      <c r="I215" s="2">
-        <v>0</v>
-      </c>
-      <c r="J215" s="2" t="s">
-        <v>185</v>
+      <c r="E216" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="F216" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="G216" s="2">
+        <v>28.4</v>
+      </c>
+      <c r="H216" s="2">
+        <v>0</v>
+      </c>
+      <c r="I216" s="2">
+        <v>0</v>
+      </c>
+      <c r="J216" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="217" spans="1:10">
+      <c r="A217" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B217" s="2">
+        <v>46028.33280092593</v>
+      </c>
+      <c r="C217" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D217" s="2">
+        <v>46028.66993055555</v>
+      </c>
+      <c r="E217" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="F217" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="G217" s="2">
+        <v>20.2</v>
+      </c>
+      <c r="H217" s="2">
+        <v>0</v>
+      </c>
+      <c r="I217" s="2">
+        <v>0</v>
+      </c>
+      <c r="J217" s="2" t="s">
+        <v>187</v>
       </c>
     </row>
   </sheetData>
